--- a/APS_BF_SMS_RM.xlsx
+++ b/APS_BF_SMS_RM.xlsx
@@ -42,8 +42,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -339,7 +340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -464,6 +465,10 @@
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -971,8 +976,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -1034,8 +1037,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -1097,8 +1098,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -1160,8 +1159,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -1223,8 +1220,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -1286,8 +1281,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -1349,8 +1342,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -1412,8 +1403,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -1475,8 +1464,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -1538,8 +1525,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -1601,8 +1586,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -1664,8 +1647,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -1727,8 +1708,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -1790,8 +1769,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -1853,8 +1830,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -1895,8 +1870,6 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>flag</t>
@@ -1912,8 +1885,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -1975,8 +1946,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -2038,8 +2007,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -2101,8 +2068,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -2164,8 +2129,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -2227,8 +2190,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -2290,8 +2251,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -2353,8 +2312,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -2416,8 +2373,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -2479,8 +2434,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -2542,8 +2495,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -2605,8 +2556,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -2649,9 +2598,6 @@
           <t>List</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Grades that use BIL-130</t>
@@ -2662,8 +2608,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -2706,9 +2650,6 @@
           <t>List</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Grades requiring VD degassing</t>
@@ -2719,8 +2660,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -2782,8 +2721,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -2845,8 +2782,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -2908,8 +2843,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -2952,8 +2885,6 @@
           <t>List</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>order</t>
@@ -2969,8 +2900,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -3013,8 +2942,6 @@
           <t>Choice</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>mode</t>
@@ -3030,8 +2957,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -3074,9 +2999,6 @@
           <t>List</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Which Flow_Type values count as inputs</t>
@@ -3087,8 +3009,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -3131,9 +3051,6 @@
           <t>List</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Which Flow_Type values are byproducts</t>
@@ -3144,8 +3061,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -3207,8 +3122,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -3270,8 +3183,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -3333,8 +3244,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -3396,8 +3305,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -3459,8 +3366,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -3522,8 +3427,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -3585,8 +3488,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -3648,8 +3549,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -3711,8 +3610,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -3774,8 +3671,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>2026-04-04</t>
@@ -48855,10 +48750,8 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="J309" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
+      <c r="J309" s="50" t="n">
+        <v>46122</v>
       </c>
       <c r="K309" s="4" t="inlineStr">
         <is>
@@ -49101,6 +48994,9 @@
         <is>
           <t>Open</t>
         </is>
+      </c>
+      <c r="J313" s="51" t="n">
+        <v>46122</v>
       </c>
     </row>
   </sheetData>

--- a/APS_BF_SMS_RM.xlsx
+++ b/APS_BF_SMS_RM.xlsx
@@ -29740,7 +29740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N313"/>
+  <dimension ref="A1:N311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="9" customWidth="1" style="39" min="1" max="1"/>
@@ -48892,111 +48892,6 @@
         <is>
           <t>Backlog</t>
         </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>SO-306</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>Kalyani Carpenter</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>FG-WR-CHQ1006-55</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>CHQ 1006</t>
-        </is>
-      </c>
-      <c r="F312" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G312" t="n">
-        <v>60</v>
-      </c>
-      <c r="H312" t="n">
-        <v>30</v>
-      </c>
-      <c r="I312" s="48" t="n">
-        <v>46116</v>
-      </c>
-      <c r="J312" s="48" t="n">
-        <v>46122</v>
-      </c>
-      <c r="K312" t="inlineStr">
-        <is>
-          <t>URGENT</t>
-        </is>
-      </c>
-      <c r="L312" t="inlineStr">
-        <is>
-          <t>CHQ-RUSH</t>
-        </is>
-      </c>
-      <c r="N312" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>SO-306</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>Kalyani Carpenter</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>FG-WR-CHQ1006-55</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>CHQ 1006</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>5.5mm</t>
-        </is>
-      </c>
-      <c r="F313" t="n">
-        <v>60</v>
-      </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t>URGENT</t>
-        </is>
-      </c>
-      <c r="I313" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="J313" s="51" t="n">
-        <v>46122</v>
       </c>
     </row>
   </sheetData>

--- a/APS_BF_SMS_RM.xlsx
+++ b/APS_BF_SMS_RM.xlsx
@@ -8217,7 +8217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18" customWidth="1" style="39" min="1" max="4"/>
@@ -8467,6 +8467,86 @@
       <c r="D12" t="inlineStr">
         <is>
           <t>2026-04-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>REQ-1775322199163</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FG-WR-SAE1080-55</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>120</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>REQ-1775322214774</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FG-WR-SAE1080-55</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>120</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>REQ-1775322228329</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FG-WR-SAE1008-55</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>120</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>REQ-1775452162143</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FG-WR-SAE1008-65</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>

--- a/APS_BF_SMS_RM.xlsx
+++ b/APS_BF_SMS_RM.xlsx
@@ -3699,7 +3699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P51"/>
+  <dimension ref="A1:P76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="26" customWidth="1" style="39" min="1" max="1"/>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>RM-01</t>
+          <t>RM-02</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>RM-01</t>
+          <t>RM-02</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>RM-01</t>
+          <t>RM-02</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>RM-01</t>
+          <t>RM-02</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>RM-01</t>
+          <t>RM-02</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>RM-01</t>
+          <t>RM-02</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>RM-01</t>
+          <t>RM-02</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>RM-01</t>
+          <t>RM-02</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>CCM-01</t>
+          <t>CCM-02</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
@@ -6896,6 +6896,431 @@
       <c r="O51" s="4" t="n"/>
       <c r="P51" s="4" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>RM-OUT-SAE1008-55</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>RM-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>RM-OUT-SAE1008-65</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>RM-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>RM-OUT-SAE1008-80</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>RM-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>RM-OUT-SAE1018-55</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>RM-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>RM-OUT-SAE1018-65</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>RM-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>RM-OUT-SAE1018-80</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>RM-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>RM-OUT-SAE1018-100</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>RM-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>RM-OUT-SAE1018-120</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>RM-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>RM-OUT-SAE1035-65</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>RM-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>RM-OUT-SAE1035-80</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>RM-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>RM-OUT-SAE1045-65</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>RM-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>RM-OUT-SAE1045-80</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>RM-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>RM-OUT-SAE1045-100</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>RM-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>RM-OUT-SAE1065-55</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>RM-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>RM-OUT-SAE1065-65</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>RM-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>RM-OUT-SAE1080-55</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>RM-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>RM-OUT-SAE1080-65</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>RM-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>RM-OUT-CHQ1006-55</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>RM-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>RM-OUT-CHQ1006-65</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>RM-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>RM-OUT-CrMo4140-80</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>RM-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>RM-OUT-CrMo4140-100</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>RM-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>VD-OUT-SAE1065</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Degassing</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>VD-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>VD-OUT-SAE1080</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Degassing</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>VD-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>VD-OUT-CHQ1006</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Degassing</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>VD-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>VD-OUT-CrMo4140</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Degassing</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>VD-01</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -8217,7 +8642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18" customWidth="1" style="39" min="1" max="4"/>
@@ -8545,6 +8970,26 @@
         <v>1</v>
       </c>
       <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>REQ-1775465786479</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>FG-WR-SAE1008-80</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>12</v>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
@@ -30007,7 +30452,7 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>CMP-003</t>
+          <t>CMP-002</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -30247,7 +30692,11 @@
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M10" s="11" t="n"/>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>CMP-005</t>
+        </is>
+      </c>
       <c r="N10" s="11" t="inlineStr">
         <is>
           <t>Open</t>
@@ -30311,7 +30760,7 @@
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
-          <t>CMP-003</t>
+          <t>CMP-007</t>
         </is>
       </c>
       <c r="N11" s="10" t="inlineStr">

--- a/APS_BF_SMS_RM.xlsx
+++ b/APS_BF_SMS_RM.xlsx
@@ -8549,7 +8549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18" customWidth="1" style="35" min="1" max="4"/>
@@ -8899,6 +8899,23 @@
       <c r="D17" t="inlineStr">
         <is>
           <t>2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>REQ-1775562304948</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FG-WR-SAE1008-80</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>

--- a/APS_BF_SMS_RM.xlsx
+++ b/APS_BF_SMS_RM.xlsx
@@ -9769,17 +9769,17 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Workbook_Name</t>
+          <t>ROLLING_MODE_DEFAULT</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>aps_bf_sms_rm</t>
+          <t>HOT</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Workbook identity used by runtime support checks.</t>
+          <t>Default rolling mode for all orders: HOT (first CCM) or COLD (last CCM). Overridable per order.</t>
         </is>
       </c>
     </row>
@@ -12476,7 +12476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M98"/>
+  <dimension ref="A1:N98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" customWidth="1" style="35" min="1" max="1"/>
@@ -12573,6 +12573,11 @@
           <t>Attribute_1</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Product_Type</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -12630,6 +12635,11 @@
       <c r="M4" s="5" t="n">
         <v>5.5</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>FINISHED_GOODS</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -12687,6 +12697,11 @@
       <c r="M5" s="5" t="n">
         <v>6.5</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>FINISHED_GOODS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -12744,6 +12759,11 @@
       <c r="M6" s="5" t="n">
         <v>8</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>FINISHED_GOODS</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -12801,6 +12821,11 @@
       <c r="M7" s="5" t="n">
         <v>5.5</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>FINISHED_GOODS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -12858,6 +12883,11 @@
       <c r="M8" s="5" t="n">
         <v>6.5</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>FINISHED_GOODS</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -12915,6 +12945,11 @@
       <c r="M9" s="5" t="n">
         <v>8</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>FINISHED_GOODS</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -12972,6 +13007,11 @@
       <c r="M10" s="5" t="n">
         <v>10</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>FINISHED_GOODS</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -13029,6 +13069,11 @@
       <c r="M11" s="5" t="n">
         <v>12</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>FINISHED_GOODS</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -13086,6 +13131,11 @@
       <c r="M12" s="5" t="n">
         <v>6.5</v>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>FINISHED_GOODS</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -13143,6 +13193,11 @@
       <c r="M13" s="5" t="n">
         <v>8</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>FINISHED_GOODS</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -13200,6 +13255,11 @@
       <c r="M14" s="5" t="n">
         <v>6.5</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>FINISHED_GOODS</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -13257,6 +13317,11 @@
       <c r="M15" s="5" t="n">
         <v>8</v>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>FINISHED_GOODS</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -13314,6 +13379,11 @@
       <c r="M16" s="5" t="n">
         <v>10</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>FINISHED_GOODS</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -13371,6 +13441,11 @@
       <c r="M17" s="5" t="n">
         <v>5.5</v>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>FINISHED_GOODS</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -13428,6 +13503,11 @@
       <c r="M18" s="5" t="n">
         <v>6.5</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>FINISHED_GOODS</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -13485,6 +13565,11 @@
       <c r="M19" s="5" t="n">
         <v>5.5</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>FINISHED_GOODS</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -13542,6 +13627,11 @@
       <c r="M20" s="5" t="n">
         <v>6.5</v>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>FINISHED_GOODS</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -13597,6 +13687,11 @@
       <c r="M21" s="5" t="n">
         <v>5.5</v>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>FINISHED_GOODS</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -13654,6 +13749,11 @@
       <c r="M22" s="5" t="n">
         <v>6.5</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>FINISHED_GOODS</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -13711,6 +13811,11 @@
       <c r="M23" s="5" t="n">
         <v>8</v>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>FINISHED_GOODS</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -13768,6 +13873,11 @@
       <c r="M24" s="5" t="n">
         <v>10</v>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>FINISHED_GOODS</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -13825,6 +13935,11 @@
       <c r="M25" s="6" t="n">
         <v>5.5</v>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -13882,6 +13997,11 @@
       <c r="M26" s="6" t="n">
         <v>6.5</v>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -13939,6 +14059,11 @@
       <c r="M27" s="6" t="n">
         <v>8</v>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -13996,6 +14121,11 @@
       <c r="M28" s="6" t="n">
         <v>5.5</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -14053,6 +14183,11 @@
       <c r="M29" s="6" t="n">
         <v>6.5</v>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -14110,6 +14245,11 @@
       <c r="M30" s="6" t="n">
         <v>8</v>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -14167,6 +14307,11 @@
       <c r="M31" s="6" t="n">
         <v>10</v>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -14224,6 +14369,11 @@
       <c r="M32" s="6" t="n">
         <v>12</v>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -14281,6 +14431,11 @@
       <c r="M33" s="6" t="n">
         <v>6.5</v>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -14338,6 +14493,11 @@
       <c r="M34" s="6" t="n">
         <v>8</v>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -14395,6 +14555,11 @@
       <c r="M35" s="6" t="n">
         <v>6.5</v>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -14452,6 +14617,11 @@
       <c r="M36" s="6" t="n">
         <v>8</v>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -14509,6 +14679,11 @@
       <c r="M37" s="6" t="n">
         <v>10</v>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -14566,6 +14741,11 @@
       <c r="M38" s="6" t="n">
         <v>5.5</v>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -14623,6 +14803,11 @@
       <c r="M39" s="6" t="n">
         <v>6.5</v>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -14680,6 +14865,11 @@
       <c r="M40" s="6" t="n">
         <v>5.5</v>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -14737,6 +14927,11 @@
       <c r="M41" s="6" t="n">
         <v>6.5</v>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -14794,6 +14989,11 @@
       <c r="M42" s="6" t="n">
         <v>5.5</v>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -14851,6 +15051,11 @@
       <c r="M43" s="6" t="n">
         <v>6.5</v>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -14908,6 +15113,11 @@
       <c r="M44" s="6" t="n">
         <v>8</v>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -14965,6 +15175,11 @@
       <c r="M45" s="6" t="n">
         <v>10</v>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -15018,6 +15233,11 @@
         </is>
       </c>
       <c r="M46" s="7" t="n"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
@@ -15071,6 +15291,11 @@
         </is>
       </c>
       <c r="M47" s="7" t="n"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
@@ -15124,6 +15349,11 @@
         </is>
       </c>
       <c r="M48" s="7" t="n"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -15177,6 +15407,11 @@
         </is>
       </c>
       <c r="M49" s="7" t="n"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -15230,6 +15465,11 @@
         </is>
       </c>
       <c r="M50" s="7" t="n"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
@@ -15283,6 +15523,11 @@
         </is>
       </c>
       <c r="M51" s="7" t="n"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
@@ -15336,6 +15581,11 @@
         </is>
       </c>
       <c r="M52" s="7" t="n"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
@@ -15389,6 +15639,11 @@
         </is>
       </c>
       <c r="M53" s="7" t="n"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>PRODUCTION_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -15446,6 +15701,11 @@
         </is>
       </c>
       <c r="M54" s="6" t="n"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -15503,6 +15763,11 @@
         </is>
       </c>
       <c r="M55" s="6" t="n"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>PROCESS_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -15560,6 +15825,11 @@
         </is>
       </c>
       <c r="M56" s="6" t="n"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>PROCESS_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -15617,6 +15887,11 @@
         </is>
       </c>
       <c r="M57" s="6" t="n"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -15674,6 +15949,11 @@
         </is>
       </c>
       <c r="M58" s="6" t="n"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>PROCESS_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -15731,6 +16011,11 @@
         </is>
       </c>
       <c r="M59" s="6" t="n"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>PROCESS_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -15788,6 +16073,11 @@
         </is>
       </c>
       <c r="M60" s="6" t="n"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
@@ -15845,6 +16135,11 @@
         </is>
       </c>
       <c r="M61" s="6" t="n"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>PROCESS_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -15902,6 +16197,11 @@
         </is>
       </c>
       <c r="M62" s="6" t="n"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>PROCESS_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -15959,6 +16259,11 @@
         </is>
       </c>
       <c r="M63" s="6" t="n"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
@@ -16016,6 +16321,11 @@
         </is>
       </c>
       <c r="M64" s="6" t="n"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>PROCESS_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -16073,6 +16383,11 @@
         </is>
       </c>
       <c r="M65" s="6" t="n"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>PROCESS_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -16130,6 +16445,11 @@
         </is>
       </c>
       <c r="M66" s="6" t="n"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
@@ -16187,6 +16507,11 @@
         </is>
       </c>
       <c r="M67" s="6" t="n"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>PROCESS_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -16244,6 +16569,11 @@
         </is>
       </c>
       <c r="M68" s="6" t="n"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>PROCESS_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -16301,6 +16631,11 @@
         </is>
       </c>
       <c r="M69" s="6" t="n"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -16358,6 +16693,11 @@
         </is>
       </c>
       <c r="M70" s="6" t="n"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>PROCESS_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -16415,6 +16755,11 @@
         </is>
       </c>
       <c r="M71" s="6" t="n"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>PROCESS_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -16472,6 +16817,11 @@
         </is>
       </c>
       <c r="M72" s="6" t="n"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>PROCESS_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
@@ -16529,6 +16879,11 @@
         </is>
       </c>
       <c r="M73" s="6" t="n"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
@@ -16586,6 +16941,11 @@
         </is>
       </c>
       <c r="M74" s="6" t="n"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>PROCESS_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -16643,6 +17003,11 @@
         </is>
       </c>
       <c r="M75" s="6" t="n"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>PROCESS_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
@@ -16700,6 +17065,11 @@
         </is>
       </c>
       <c r="M76" s="6" t="n"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>PROCESS_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -16757,6 +17127,11 @@
         </is>
       </c>
       <c r="M77" s="6" t="n"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
@@ -16814,6 +17189,11 @@
         </is>
       </c>
       <c r="M78" s="6" t="n"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>PROCESS_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
@@ -16871,6 +17251,11 @@
         </is>
       </c>
       <c r="M79" s="6" t="n"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>PROCESS_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
@@ -16928,6 +17313,11 @@
         </is>
       </c>
       <c r="M80" s="6" t="n"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>PROCESS_INTERMEDIATE</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
@@ -16981,6 +17371,11 @@
       </c>
       <c r="L81" s="6" t="n"/>
       <c r="M81" s="6" t="n"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>RAW_MATERIAL</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
@@ -17034,6 +17429,11 @@
       </c>
       <c r="L82" s="6" t="n"/>
       <c r="M82" s="6" t="n"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>RAW_MATERIAL</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
@@ -17087,6 +17487,11 @@
       </c>
       <c r="L83" s="8" t="n"/>
       <c r="M83" s="8" t="n"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>RAW_MATERIAL</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
@@ -17140,6 +17545,11 @@
       </c>
       <c r="L84" s="8" t="n"/>
       <c r="M84" s="8" t="n"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
@@ -17193,6 +17603,11 @@
       </c>
       <c r="L85" s="8" t="n"/>
       <c r="M85" s="8" t="n"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
@@ -17246,6 +17661,11 @@
       </c>
       <c r="L86" s="8" t="n"/>
       <c r="M86" s="8" t="n"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
@@ -17299,6 +17719,11 @@
       </c>
       <c r="L87" s="8" t="n"/>
       <c r="M87" s="8" t="n"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
@@ -17352,6 +17777,11 @@
       </c>
       <c r="L88" s="8" t="n"/>
       <c r="M88" s="8" t="n"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>RAW_MATERIAL</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
@@ -17405,6 +17835,11 @@
       </c>
       <c r="L89" s="8" t="n"/>
       <c r="M89" s="8" t="n"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>RAW_MATERIAL</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
@@ -17458,6 +17893,11 @@
       </c>
       <c r="L90" s="9" t="n"/>
       <c r="M90" s="9" t="n"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>RAW_MATERIAL</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
@@ -17511,6 +17951,11 @@
       </c>
       <c r="L91" s="9" t="n"/>
       <c r="M91" s="9" t="n"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>RAW_MATERIAL</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
@@ -17564,6 +18009,11 @@
       </c>
       <c r="L92" s="9" t="n"/>
       <c r="M92" s="9" t="n"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>RAW_MATERIAL</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
@@ -17617,6 +18067,11 @@
       </c>
       <c r="L93" s="9" t="n"/>
       <c r="M93" s="9" t="n"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>RAW_MATERIAL</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
@@ -17670,6 +18125,11 @@
       </c>
       <c r="L94" s="9" t="n"/>
       <c r="M94" s="9" t="n"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>RAW_MATERIAL</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
@@ -17723,6 +18183,11 @@
       </c>
       <c r="L95" s="9" t="n"/>
       <c r="M95" s="9" t="n"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>RAW_MATERIAL</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
@@ -17776,6 +18241,11 @@
       </c>
       <c r="L96" s="9" t="n"/>
       <c r="M96" s="9" t="n"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>RAW_MATERIAL</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
@@ -17829,6 +18299,11 @@
       </c>
       <c r="L97" s="9" t="n"/>
       <c r="M97" s="9" t="n"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>RAW_MATERIAL</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
@@ -17882,6 +18357,11 @@
       </c>
       <c r="L98" s="9" t="n"/>
       <c r="M98" s="9" t="n"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>RAW_MATERIAL</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -30189,7 +30669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N308"/>
+  <dimension ref="A1:P308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="9" customWidth="1" style="35" min="1" max="1"/>
@@ -30277,17 +30757,27 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Order_Type</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Rolling_Mode</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Campaign_Group</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>Campaign_ID</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -30343,17 +30833,27 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>MTO</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>CMP-002</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -30409,17 +30909,17 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>CMP-001</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -30475,17 +30975,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L6" s="10" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M6" s="10" t="inlineStr">
+      <c r="O6" s="10" t="inlineStr">
         <is>
           <t>PO-0009</t>
         </is>
       </c>
-      <c r="N6" s="10" t="inlineStr">
+      <c r="P6" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -30541,17 +31041,17 @@
           <t>URGENT</t>
         </is>
       </c>
-      <c r="L7" s="11" t="inlineStr">
+      <c r="N7" s="11" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M7" s="11" t="inlineStr">
+      <c r="O7" s="11" t="inlineStr">
         <is>
           <t>PO-0007</t>
         </is>
       </c>
-      <c r="N7" s="11" t="inlineStr">
+      <c r="P7" s="11" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -30607,17 +31107,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L8" s="10" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="O8" s="10" t="inlineStr">
         <is>
           <t>PO-0018</t>
         </is>
       </c>
-      <c r="N8" s="10" t="inlineStr">
+      <c r="P8" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -30673,13 +31173,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -30735,13 +31235,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="n"/>
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -30797,17 +31297,17 @@
           <t>URGENT</t>
         </is>
       </c>
-      <c r="L11" s="11" t="inlineStr">
+      <c r="N11" s="11" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M11" s="11" t="inlineStr">
+      <c r="O11" s="11" t="inlineStr">
         <is>
           <t>PO-0003</t>
         </is>
       </c>
-      <c r="N11" s="11" t="inlineStr">
+      <c r="P11" s="11" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -30863,17 +31363,17 @@
           <t>URGENT</t>
         </is>
       </c>
-      <c r="L12" s="11" t="inlineStr">
+      <c r="N12" s="11" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M12" s="11" t="inlineStr">
+      <c r="O12" s="11" t="inlineStr">
         <is>
           <t>PO-0008</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr">
+      <c r="P12" s="11" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -30929,17 +31429,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L13" s="10" t="inlineStr">
+      <c r="N13" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M13" s="10" t="inlineStr">
+      <c r="O13" s="10" t="inlineStr">
         <is>
           <t>PO-0014</t>
         </is>
       </c>
-      <c r="N13" s="10" t="inlineStr">
+      <c r="P13" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -30995,13 +31495,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -31057,17 +31557,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L15" s="10" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M15" s="10" t="inlineStr">
+      <c r="O15" s="10" t="inlineStr">
         <is>
           <t>PO-0013</t>
         </is>
       </c>
-      <c r="N15" s="10" t="inlineStr">
+      <c r="P15" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -31123,13 +31623,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="n"/>
+      <c r="P16" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -31185,17 +31685,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L17" s="10" t="inlineStr">
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M17" s="10" t="inlineStr">
+      <c r="O17" s="10" t="inlineStr">
         <is>
           <t>PO-0022</t>
         </is>
       </c>
-      <c r="N17" s="10" t="inlineStr">
+      <c r="P17" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -31251,13 +31751,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M18" s="4" t="n"/>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -31313,13 +31813,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M19" s="4" t="n"/>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -31375,17 +31875,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L20" s="10" t="inlineStr">
+      <c r="N20" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M20" s="10" t="inlineStr">
+      <c r="O20" s="10" t="inlineStr">
         <is>
           <t>PO-0007</t>
         </is>
       </c>
-      <c r="N20" s="10" t="inlineStr">
+      <c r="P20" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -31441,13 +31941,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M21" s="4" t="n"/>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -31503,13 +32003,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M22" s="4" t="n"/>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="O22" s="4" t="n"/>
+      <c r="P22" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -31565,17 +32065,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L23" s="10" t="inlineStr">
+      <c r="N23" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M23" s="10" t="inlineStr">
+      <c r="O23" s="10" t="inlineStr">
         <is>
           <t>PO-0012</t>
         </is>
       </c>
-      <c r="N23" s="10" t="inlineStr">
+      <c r="P23" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -31631,17 +32131,17 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>PO-0021</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="P24" s="4" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -31697,13 +32197,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr">
+      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M25" s="4" t="n"/>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="O25" s="4" t="n"/>
+      <c r="P25" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -31759,13 +32259,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="N26" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M26" s="4" t="n"/>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="O26" s="4" t="n"/>
+      <c r="P26" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -31821,17 +32321,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L27" s="10" t="inlineStr">
+      <c r="N27" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M27" s="10" t="inlineStr">
+      <c r="O27" s="10" t="inlineStr">
         <is>
           <t>PO-0006</t>
         </is>
       </c>
-      <c r="N27" s="10" t="inlineStr">
+      <c r="P27" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -31887,13 +32387,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L28" s="4" t="inlineStr">
+      <c r="N28" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M28" s="4" t="n"/>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="O28" s="4" t="n"/>
+      <c r="P28" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -31949,17 +32449,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L29" s="10" t="inlineStr">
+      <c r="N29" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M29" s="10" t="inlineStr">
+      <c r="O29" s="10" t="inlineStr">
         <is>
           <t>PO-0008</t>
         </is>
       </c>
-      <c r="N29" s="10" t="inlineStr">
+      <c r="P29" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -32015,13 +32515,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L30" s="4" t="inlineStr">
+      <c r="N30" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="O30" s="4" t="n"/>
+      <c r="P30" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -32077,17 +32577,17 @@
           <t>URGENT</t>
         </is>
       </c>
-      <c r="L31" s="11" t="inlineStr">
+      <c r="N31" s="11" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M31" s="11" t="inlineStr">
+      <c r="O31" s="11" t="inlineStr">
         <is>
           <t>PO-0001</t>
         </is>
       </c>
-      <c r="N31" s="11" t="inlineStr">
+      <c r="P31" s="11" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -32143,17 +32643,17 @@
           <t>URGENT</t>
         </is>
       </c>
-      <c r="L32" s="11" t="inlineStr">
+      <c r="N32" s="11" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M32" s="11" t="inlineStr">
+      <c r="O32" s="11" t="inlineStr">
         <is>
           <t>PO-0004</t>
         </is>
       </c>
-      <c r="N32" s="11" t="inlineStr">
+      <c r="P32" s="11" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -32209,17 +32709,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L33" s="10" t="inlineStr">
+      <c r="N33" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M33" s="10" t="inlineStr">
+      <c r="O33" s="10" t="inlineStr">
         <is>
           <t>PO-0010</t>
         </is>
       </c>
-      <c r="N33" s="10" t="inlineStr">
+      <c r="P33" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -32275,17 +32775,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L34" s="10" t="inlineStr">
+      <c r="N34" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M34" s="10" t="inlineStr">
+      <c r="O34" s="10" t="inlineStr">
         <is>
           <t>PO-0011</t>
         </is>
       </c>
-      <c r="N34" s="10" t="inlineStr">
+      <c r="P34" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -32341,17 +32841,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L35" s="10" t="inlineStr">
+      <c r="N35" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M35" s="10" t="inlineStr">
+      <c r="O35" s="10" t="inlineStr">
         <is>
           <t>PO-0015</t>
         </is>
       </c>
-      <c r="N35" s="10" t="inlineStr">
+      <c r="P35" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -32407,17 +32907,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L36" s="10" t="inlineStr">
+      <c r="N36" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M36" s="10" t="inlineStr">
+      <c r="O36" s="10" t="inlineStr">
         <is>
           <t>PO-0019</t>
         </is>
       </c>
-      <c r="N36" s="10" t="inlineStr">
+      <c r="P36" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -32473,17 +32973,17 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L37" s="4" t="inlineStr">
+      <c r="N37" s="4" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M37" s="4" t="inlineStr">
+      <c r="O37" s="4" t="inlineStr">
         <is>
           <t>PO-0026</t>
         </is>
       </c>
-      <c r="N37" s="4" t="inlineStr">
+      <c r="P37" s="4" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -32539,17 +33039,17 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L38" s="4" t="inlineStr">
+      <c r="N38" s="4" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M38" s="4" t="inlineStr">
+      <c r="O38" s="4" t="inlineStr">
         <is>
           <t>PO-0025</t>
         </is>
       </c>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="P38" s="4" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -32605,17 +33105,17 @@
           <t>URGENT</t>
         </is>
       </c>
-      <c r="L39" s="11" t="inlineStr">
+      <c r="N39" s="11" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M39" s="11" t="inlineStr">
+      <c r="O39" s="11" t="inlineStr">
         <is>
           <t>PO-0002</t>
         </is>
       </c>
-      <c r="N39" s="11" t="inlineStr">
+      <c r="P39" s="11" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -32671,17 +33171,17 @@
           <t>URGENT</t>
         </is>
       </c>
-      <c r="L40" s="11" t="inlineStr">
+      <c r="N40" s="11" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M40" s="11" t="inlineStr">
+      <c r="O40" s="11" t="inlineStr">
         <is>
           <t>PO-0005</t>
         </is>
       </c>
-      <c r="N40" s="11" t="inlineStr">
+      <c r="P40" s="11" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -32737,17 +33237,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L41" s="10" t="inlineStr">
+      <c r="N41" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M41" s="10" t="inlineStr">
+      <c r="O41" s="10" t="inlineStr">
         <is>
           <t>PO-0023</t>
         </is>
       </c>
-      <c r="N41" s="10" t="inlineStr">
+      <c r="P41" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -32803,17 +33303,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L42" s="10" t="inlineStr">
+      <c r="N42" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M42" s="10" t="inlineStr">
+      <c r="O42" s="10" t="inlineStr">
         <is>
           <t>PO-0020</t>
         </is>
       </c>
-      <c r="N42" s="10" t="inlineStr">
+      <c r="P42" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -32869,17 +33369,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L43" s="10" t="inlineStr">
+      <c r="N43" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M43" s="10" t="inlineStr">
+      <c r="O43" s="10" t="inlineStr">
         <is>
           <t>PO-0003</t>
         </is>
       </c>
-      <c r="N43" s="10" t="inlineStr">
+      <c r="P43" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -32935,17 +33435,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L44" s="10" t="inlineStr">
+      <c r="N44" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M44" s="10" t="inlineStr">
+      <c r="O44" s="10" t="inlineStr">
         <is>
           <t>PO-0018</t>
         </is>
       </c>
-      <c r="N44" s="10" t="inlineStr">
+      <c r="P44" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -33001,13 +33501,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L45" s="4" t="inlineStr">
+      <c r="N45" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M45" s="4" t="n"/>
-      <c r="N45" s="4" t="inlineStr">
+      <c r="O45" s="4" t="n"/>
+      <c r="P45" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -33063,13 +33563,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L46" s="4" t="inlineStr">
+      <c r="N46" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M46" s="4" t="n"/>
-      <c r="N46" s="4" t="inlineStr">
+      <c r="O46" s="4" t="n"/>
+      <c r="P46" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -33125,17 +33625,17 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L47" s="4" t="inlineStr">
+      <c r="N47" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M47" s="4" t="inlineStr">
+      <c r="O47" s="4" t="inlineStr">
         <is>
           <t>BIG-1018</t>
         </is>
       </c>
-      <c r="N47" s="4" t="inlineStr">
+      <c r="P47" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -33191,17 +33691,17 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L48" s="4" t="inlineStr">
+      <c r="N48" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M48" s="4" t="inlineStr">
+      <c r="O48" s="4" t="inlineStr">
         <is>
           <t>BIG-1018</t>
         </is>
       </c>
-      <c r="N48" s="4" t="inlineStr">
+      <c r="P48" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -33257,17 +33757,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L49" s="10" t="inlineStr">
+      <c r="N49" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M49" s="10" t="inlineStr">
+      <c r="O49" s="10" t="inlineStr">
         <is>
           <t>PO-0012</t>
         </is>
       </c>
-      <c r="N49" s="10" t="inlineStr">
+      <c r="P49" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -33323,17 +33823,17 @@
           <t>URGENT</t>
         </is>
       </c>
-      <c r="L50" s="11" t="inlineStr">
+      <c r="N50" s="11" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M50" s="11" t="inlineStr">
+      <c r="O50" s="11" t="inlineStr">
         <is>
           <t>PO-0006</t>
         </is>
       </c>
-      <c r="N50" s="11" t="inlineStr">
+      <c r="P50" s="11" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -33389,17 +33889,17 @@
           <t>URGENT</t>
         </is>
       </c>
-      <c r="L51" s="11" t="inlineStr">
+      <c r="N51" s="11" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M51" s="11" t="inlineStr">
+      <c r="O51" s="11" t="inlineStr">
         <is>
           <t>PO-0009</t>
         </is>
       </c>
-      <c r="N51" s="11" t="inlineStr">
+      <c r="P51" s="11" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -33455,17 +33955,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L52" s="10" t="inlineStr">
+      <c r="N52" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M52" s="10" t="inlineStr">
+      <c r="O52" s="10" t="inlineStr">
         <is>
           <t>PO-0005</t>
         </is>
       </c>
-      <c r="N52" s="10" t="inlineStr">
+      <c r="P52" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -33521,17 +34021,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L53" s="10" t="inlineStr">
+      <c r="N53" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M53" s="10" t="inlineStr">
+      <c r="O53" s="10" t="inlineStr">
         <is>
           <t>PO-0016</t>
         </is>
       </c>
-      <c r="N53" s="10" t="inlineStr">
+      <c r="P53" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -33587,17 +34087,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L54" s="10" t="inlineStr">
+      <c r="N54" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M54" s="10" t="inlineStr">
+      <c r="O54" s="10" t="inlineStr">
         <is>
           <t>PO-0013</t>
         </is>
       </c>
-      <c r="N54" s="10" t="inlineStr">
+      <c r="P54" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -33653,17 +34153,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L55" s="10" t="inlineStr">
+      <c r="N55" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M55" s="10" t="inlineStr">
+      <c r="O55" s="10" t="inlineStr">
         <is>
           <t>PO-0017</t>
         </is>
       </c>
-      <c r="N55" s="10" t="inlineStr">
+      <c r="P55" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -33719,17 +34219,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L56" s="10" t="inlineStr">
+      <c r="N56" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M56" s="10" t="inlineStr">
+      <c r="O56" s="10" t="inlineStr">
         <is>
           <t>PO-0014</t>
         </is>
       </c>
-      <c r="N56" s="10" t="inlineStr">
+      <c r="P56" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -33785,17 +34285,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L57" s="10" t="inlineStr">
+      <c r="N57" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M57" s="10" t="inlineStr">
+      <c r="O57" s="10" t="inlineStr">
         <is>
           <t>PO-0020</t>
         </is>
       </c>
-      <c r="N57" s="10" t="inlineStr">
+      <c r="P57" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -33851,17 +34351,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L58" s="10" t="inlineStr">
+      <c r="N58" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M58" s="10" t="inlineStr">
+      <c r="O58" s="10" t="inlineStr">
         <is>
           <t>PO-0024</t>
         </is>
       </c>
-      <c r="N58" s="10" t="inlineStr">
+      <c r="P58" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -33917,17 +34417,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L59" s="10" t="inlineStr">
+      <c r="N59" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M59" s="10" t="inlineStr">
+      <c r="O59" s="10" t="inlineStr">
         <is>
           <t>PO-0021</t>
         </is>
       </c>
-      <c r="N59" s="10" t="inlineStr">
+      <c r="P59" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -33983,17 +34483,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L60" s="10" t="inlineStr">
+      <c r="N60" s="10" t="inlineStr">
         <is>
           <t>APS_RELEASED</t>
         </is>
       </c>
-      <c r="M60" s="10" t="inlineStr">
+      <c r="O60" s="10" t="inlineStr">
         <is>
           <t>PO-0010</t>
         </is>
       </c>
-      <c r="N60" s="10" t="inlineStr">
+      <c r="P60" s="10" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
@@ -34049,13 +34549,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L61" s="4" t="inlineStr">
+      <c r="N61" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M61" s="4" t="n"/>
-      <c r="N61" s="4" t="inlineStr">
+      <c r="O61" s="4" t="n"/>
+      <c r="P61" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -34111,13 +34611,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L62" s="4" t="inlineStr">
+      <c r="N62" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M62" s="4" t="n"/>
-      <c r="N62" s="4" t="inlineStr">
+      <c r="O62" s="4" t="n"/>
+      <c r="P62" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -34173,13 +34673,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L63" s="10" t="inlineStr">
+      <c r="N63" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M63" s="10" t="n"/>
-      <c r="N63" s="10" t="inlineStr">
+      <c r="O63" s="10" t="n"/>
+      <c r="P63" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -34235,13 +34735,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L64" s="4" t="inlineStr">
+      <c r="N64" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M64" s="4" t="n"/>
-      <c r="N64" s="4" t="inlineStr">
+      <c r="O64" s="4" t="n"/>
+      <c r="P64" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -34297,13 +34797,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L65" s="10" t="inlineStr">
+      <c r="N65" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M65" s="10" t="n"/>
-      <c r="N65" s="10" t="inlineStr">
+      <c r="O65" s="10" t="n"/>
+      <c r="P65" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -34359,13 +34859,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L66" s="10" t="inlineStr">
+      <c r="N66" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M66" s="10" t="n"/>
-      <c r="N66" s="10" t="inlineStr">
+      <c r="O66" s="10" t="n"/>
+      <c r="P66" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -34421,13 +34921,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L67" s="4" t="inlineStr">
+      <c r="N67" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M67" s="4" t="n"/>
-      <c r="N67" s="4" t="inlineStr">
+      <c r="O67" s="4" t="n"/>
+      <c r="P67" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -34483,13 +34983,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L68" s="4" t="inlineStr">
+      <c r="N68" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M68" s="4" t="n"/>
-      <c r="N68" s="4" t="inlineStr">
+      <c r="O68" s="4" t="n"/>
+      <c r="P68" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -34545,13 +35045,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L69" s="4" t="inlineStr">
+      <c r="N69" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M69" s="4" t="n"/>
-      <c r="N69" s="4" t="inlineStr">
+      <c r="O69" s="4" t="n"/>
+      <c r="P69" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -34607,13 +35107,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L70" s="4" t="inlineStr">
+      <c r="N70" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M70" s="4" t="n"/>
-      <c r="N70" s="4" t="inlineStr">
+      <c r="O70" s="4" t="n"/>
+      <c r="P70" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -34669,13 +35169,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L71" s="4" t="inlineStr">
+      <c r="N71" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M71" s="4" t="n"/>
-      <c r="N71" s="4" t="inlineStr">
+      <c r="O71" s="4" t="n"/>
+      <c r="P71" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -34731,13 +35231,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L72" s="4" t="inlineStr">
+      <c r="N72" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M72" s="4" t="n"/>
-      <c r="N72" s="4" t="inlineStr">
+      <c r="O72" s="4" t="n"/>
+      <c r="P72" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -34793,13 +35293,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L73" s="4" t="inlineStr">
+      <c r="N73" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M73" s="4" t="n"/>
-      <c r="N73" s="4" t="inlineStr">
+      <c r="O73" s="4" t="n"/>
+      <c r="P73" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -34855,13 +35355,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L74" s="4" t="inlineStr">
+      <c r="N74" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M74" s="4" t="n"/>
-      <c r="N74" s="4" t="inlineStr">
+      <c r="O74" s="4" t="n"/>
+      <c r="P74" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -34917,13 +35417,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L75" s="4" t="inlineStr">
+      <c r="N75" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M75" s="4" t="n"/>
-      <c r="N75" s="4" t="inlineStr">
+      <c r="O75" s="4" t="n"/>
+      <c r="P75" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -34979,13 +35479,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L76" s="4" t="inlineStr">
+      <c r="N76" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M76" s="4" t="n"/>
-      <c r="N76" s="4" t="inlineStr">
+      <c r="O76" s="4" t="n"/>
+      <c r="P76" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -35041,13 +35541,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L77" s="4" t="inlineStr">
+      <c r="N77" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M77" s="4" t="n"/>
-      <c r="N77" s="4" t="inlineStr">
+      <c r="O77" s="4" t="n"/>
+      <c r="P77" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -35103,13 +35603,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L78" s="4" t="inlineStr">
+      <c r="N78" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M78" s="4" t="n"/>
-      <c r="N78" s="4" t="inlineStr">
+      <c r="O78" s="4" t="n"/>
+      <c r="P78" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -35165,13 +35665,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L79" s="4" t="inlineStr">
+      <c r="N79" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M79" s="4" t="n"/>
-      <c r="N79" s="4" t="inlineStr">
+      <c r="O79" s="4" t="n"/>
+      <c r="P79" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -35227,13 +35727,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L80" s="4" t="inlineStr">
+      <c r="N80" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M80" s="4" t="n"/>
-      <c r="N80" s="4" t="inlineStr">
+      <c r="O80" s="4" t="n"/>
+      <c r="P80" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -35289,13 +35789,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L81" s="10" t="inlineStr">
+      <c r="N81" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M81" s="10" t="n"/>
-      <c r="N81" s="10" t="inlineStr">
+      <c r="O81" s="10" t="n"/>
+      <c r="P81" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -35351,13 +35851,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L82" s="10" t="inlineStr">
+      <c r="N82" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M82" s="10" t="n"/>
-      <c r="N82" s="10" t="inlineStr">
+      <c r="O82" s="10" t="n"/>
+      <c r="P82" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -35413,13 +35913,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L83" s="10" t="inlineStr">
+      <c r="N83" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M83" s="10" t="n"/>
-      <c r="N83" s="10" t="inlineStr">
+      <c r="O83" s="10" t="n"/>
+      <c r="P83" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -35475,13 +35975,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L84" s="10" t="inlineStr">
+      <c r="N84" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M84" s="10" t="n"/>
-      <c r="N84" s="10" t="inlineStr">
+      <c r="O84" s="10" t="n"/>
+      <c r="P84" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -35537,13 +36037,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L85" s="10" t="inlineStr">
+      <c r="N85" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M85" s="10" t="n"/>
-      <c r="N85" s="10" t="inlineStr">
+      <c r="O85" s="10" t="n"/>
+      <c r="P85" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -35599,13 +36099,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L86" s="10" t="inlineStr">
+      <c r="N86" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M86" s="10" t="n"/>
-      <c r="N86" s="10" t="inlineStr">
+      <c r="O86" s="10" t="n"/>
+      <c r="P86" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -35661,13 +36161,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L87" s="10" t="inlineStr">
+      <c r="N87" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M87" s="10" t="n"/>
-      <c r="N87" s="10" t="inlineStr">
+      <c r="O87" s="10" t="n"/>
+      <c r="P87" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -35723,13 +36223,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L88" s="10" t="inlineStr">
+      <c r="N88" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M88" s="10" t="n"/>
-      <c r="N88" s="10" t="inlineStr">
+      <c r="O88" s="10" t="n"/>
+      <c r="P88" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -35785,13 +36285,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L89" s="10" t="inlineStr">
+      <c r="N89" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M89" s="10" t="n"/>
-      <c r="N89" s="10" t="inlineStr">
+      <c r="O89" s="10" t="n"/>
+      <c r="P89" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -35847,13 +36347,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L90" s="10" t="inlineStr">
+      <c r="N90" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M90" s="10" t="n"/>
-      <c r="N90" s="10" t="inlineStr">
+      <c r="O90" s="10" t="n"/>
+      <c r="P90" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -35909,13 +36409,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L91" s="10" t="inlineStr">
+      <c r="N91" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M91" s="10" t="n"/>
-      <c r="N91" s="10" t="inlineStr">
+      <c r="O91" s="10" t="n"/>
+      <c r="P91" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -35971,13 +36471,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L92" s="10" t="inlineStr">
+      <c r="N92" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M92" s="10" t="n"/>
-      <c r="N92" s="10" t="inlineStr">
+      <c r="O92" s="10" t="n"/>
+      <c r="P92" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -36033,13 +36533,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L93" s="10" t="inlineStr">
+      <c r="N93" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M93" s="10" t="n"/>
-      <c r="N93" s="10" t="inlineStr">
+      <c r="O93" s="10" t="n"/>
+      <c r="P93" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -36095,13 +36595,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L94" s="10" t="inlineStr">
+      <c r="N94" s="10" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M94" s="10" t="n"/>
-      <c r="N94" s="10" t="inlineStr">
+      <c r="O94" s="10" t="n"/>
+      <c r="P94" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -36157,13 +36657,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L95" s="10" t="inlineStr">
+      <c r="N95" s="10" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M95" s="10" t="n"/>
-      <c r="N95" s="10" t="inlineStr">
+      <c r="O95" s="10" t="n"/>
+      <c r="P95" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -36219,13 +36719,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L96" s="10" t="inlineStr">
+      <c r="N96" s="10" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M96" s="10" t="n"/>
-      <c r="N96" s="10" t="inlineStr">
+      <c r="O96" s="10" t="n"/>
+      <c r="P96" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -36281,13 +36781,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L97" s="10" t="inlineStr">
+      <c r="N97" s="10" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M97" s="10" t="n"/>
-      <c r="N97" s="10" t="inlineStr">
+      <c r="O97" s="10" t="n"/>
+      <c r="P97" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -36343,13 +36843,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L98" s="10" t="inlineStr">
+      <c r="N98" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M98" s="10" t="n"/>
-      <c r="N98" s="10" t="inlineStr">
+      <c r="O98" s="10" t="n"/>
+      <c r="P98" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -36405,13 +36905,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L99" s="10" t="inlineStr">
+      <c r="N99" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M99" s="10" t="n"/>
-      <c r="N99" s="10" t="inlineStr">
+      <c r="O99" s="10" t="n"/>
+      <c r="P99" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -36467,13 +36967,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L100" s="10" t="inlineStr">
+      <c r="N100" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M100" s="10" t="n"/>
-      <c r="N100" s="10" t="inlineStr">
+      <c r="O100" s="10" t="n"/>
+      <c r="P100" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -36529,13 +37029,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L101" s="10" t="inlineStr">
+      <c r="N101" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M101" s="10" t="n"/>
-      <c r="N101" s="10" t="inlineStr">
+      <c r="O101" s="10" t="n"/>
+      <c r="P101" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -36591,13 +37091,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L102" s="10" t="inlineStr">
+      <c r="N102" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M102" s="10" t="n"/>
-      <c r="N102" s="10" t="inlineStr">
+      <c r="O102" s="10" t="n"/>
+      <c r="P102" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -36653,13 +37153,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L103" s="10" t="inlineStr">
+      <c r="N103" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M103" s="10" t="n"/>
-      <c r="N103" s="10" t="inlineStr">
+      <c r="O103" s="10" t="n"/>
+      <c r="P103" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -36715,17 +37215,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L104" s="10" t="inlineStr">
+      <c r="N104" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M104" s="10" t="inlineStr">
+      <c r="O104" s="10" t="inlineStr">
         <is>
           <t>CMP-009</t>
         </is>
       </c>
-      <c r="N104" s="10" t="inlineStr">
+      <c r="P104" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -36781,17 +37281,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L105" s="10" t="inlineStr">
+      <c r="N105" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M105" s="10" t="inlineStr">
+      <c r="O105" s="10" t="inlineStr">
         <is>
           <t>CMP-009</t>
         </is>
       </c>
-      <c r="N105" s="10" t="inlineStr">
+      <c r="P105" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -36847,17 +37347,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L106" s="10" t="inlineStr">
+      <c r="N106" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M106" s="10" t="inlineStr">
+      <c r="O106" s="10" t="inlineStr">
         <is>
           <t>CMP-009</t>
         </is>
       </c>
-      <c r="N106" s="10" t="inlineStr">
+      <c r="P106" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -36913,17 +37413,17 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L107" s="10" t="inlineStr">
+      <c r="N107" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M107" s="10" t="inlineStr">
+      <c r="O107" s="10" t="inlineStr">
         <is>
           <t>CMP-009</t>
         </is>
       </c>
-      <c r="N107" s="10" t="inlineStr">
+      <c r="P107" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -36979,13 +37479,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L108" s="10" t="inlineStr">
+      <c r="N108" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M108" s="10" t="n"/>
-      <c r="N108" s="10" t="inlineStr">
+      <c r="O108" s="10" t="n"/>
+      <c r="P108" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -37041,13 +37541,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L109" s="10" t="inlineStr">
+      <c r="N109" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M109" s="10" t="n"/>
-      <c r="N109" s="10" t="inlineStr">
+      <c r="O109" s="10" t="n"/>
+      <c r="P109" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -37103,13 +37603,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L110" s="10" t="inlineStr">
+      <c r="N110" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M110" s="10" t="n"/>
-      <c r="N110" s="10" t="inlineStr">
+      <c r="O110" s="10" t="n"/>
+      <c r="P110" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -37165,13 +37665,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L111" s="10" t="inlineStr">
+      <c r="N111" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M111" s="10" t="n"/>
-      <c r="N111" s="10" t="inlineStr">
+      <c r="O111" s="10" t="n"/>
+      <c r="P111" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -37227,13 +37727,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L112" s="10" t="inlineStr">
+      <c r="N112" s="10" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M112" s="10" t="n"/>
-      <c r="N112" s="10" t="inlineStr">
+      <c r="O112" s="10" t="n"/>
+      <c r="P112" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -37289,13 +37789,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L113" s="10" t="inlineStr">
+      <c r="N113" s="10" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M113" s="10" t="n"/>
-      <c r="N113" s="10" t="inlineStr">
+      <c r="O113" s="10" t="n"/>
+      <c r="P113" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -37351,13 +37851,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L114" s="10" t="inlineStr">
+      <c r="N114" s="10" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M114" s="10" t="n"/>
-      <c r="N114" s="10" t="inlineStr">
+      <c r="O114" s="10" t="n"/>
+      <c r="P114" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -37413,13 +37913,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L115" s="10" t="inlineStr">
+      <c r="N115" s="10" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M115" s="10" t="n"/>
-      <c r="N115" s="10" t="inlineStr">
+      <c r="O115" s="10" t="n"/>
+      <c r="P115" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -37475,13 +37975,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L116" s="10" t="inlineStr">
+      <c r="N116" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M116" s="10" t="n"/>
-      <c r="N116" s="10" t="inlineStr">
+      <c r="O116" s="10" t="n"/>
+      <c r="P116" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -37537,13 +38037,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L117" s="4" t="inlineStr">
+      <c r="N117" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M117" s="4" t="n"/>
-      <c r="N117" s="4" t="inlineStr">
+      <c r="O117" s="4" t="n"/>
+      <c r="P117" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -37599,13 +38099,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L118" s="4" t="inlineStr">
+      <c r="N118" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M118" s="4" t="n"/>
-      <c r="N118" s="4" t="inlineStr">
+      <c r="O118" s="4" t="n"/>
+      <c r="P118" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -37661,13 +38161,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L119" s="4" t="inlineStr">
+      <c r="N119" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M119" s="4" t="n"/>
-      <c r="N119" s="4" t="inlineStr">
+      <c r="O119" s="4" t="n"/>
+      <c r="P119" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -37723,13 +38223,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L120" s="4" t="inlineStr">
+      <c r="N120" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M120" s="4" t="n"/>
-      <c r="N120" s="4" t="inlineStr">
+      <c r="O120" s="4" t="n"/>
+      <c r="P120" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -37785,13 +38285,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L121" s="4" t="inlineStr">
+      <c r="N121" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M121" s="4" t="n"/>
-      <c r="N121" s="4" t="inlineStr">
+      <c r="O121" s="4" t="n"/>
+      <c r="P121" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -37847,13 +38347,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L122" s="4" t="inlineStr">
+      <c r="N122" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M122" s="4" t="n"/>
-      <c r="N122" s="4" t="inlineStr">
+      <c r="O122" s="4" t="n"/>
+      <c r="P122" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -37909,13 +38409,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L123" s="4" t="inlineStr">
+      <c r="N123" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M123" s="4" t="n"/>
-      <c r="N123" s="4" t="inlineStr">
+      <c r="O123" s="4" t="n"/>
+      <c r="P123" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -37971,13 +38471,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L124" s="10" t="inlineStr">
+      <c r="N124" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M124" s="10" t="n"/>
-      <c r="N124" s="10" t="inlineStr">
+      <c r="O124" s="10" t="n"/>
+      <c r="P124" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -38033,13 +38533,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L125" s="10" t="inlineStr">
+      <c r="N125" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M125" s="10" t="n"/>
-      <c r="N125" s="10" t="inlineStr">
+      <c r="O125" s="10" t="n"/>
+      <c r="P125" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -38095,13 +38595,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L126" s="4" t="inlineStr">
+      <c r="N126" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M126" s="4" t="n"/>
-      <c r="N126" s="4" t="inlineStr">
+      <c r="O126" s="4" t="n"/>
+      <c r="P126" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -38157,13 +38657,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L127" s="4" t="inlineStr">
+      <c r="N127" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M127" s="4" t="n"/>
-      <c r="N127" s="4" t="inlineStr">
+      <c r="O127" s="4" t="n"/>
+      <c r="P127" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -38219,13 +38719,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L128" s="4" t="inlineStr">
+      <c r="N128" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M128" s="4" t="n"/>
-      <c r="N128" s="4" t="inlineStr">
+      <c r="O128" s="4" t="n"/>
+      <c r="P128" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -38281,13 +38781,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L129" s="10" t="inlineStr">
+      <c r="N129" s="10" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M129" s="10" t="n"/>
-      <c r="N129" s="10" t="inlineStr">
+      <c r="O129" s="10" t="n"/>
+      <c r="P129" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -38343,13 +38843,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L130" s="4" t="inlineStr">
+      <c r="N130" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M130" s="4" t="n"/>
-      <c r="N130" s="4" t="inlineStr">
+      <c r="O130" s="4" t="n"/>
+      <c r="P130" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -38405,13 +38905,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L131" s="10" t="inlineStr">
+      <c r="N131" s="10" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M131" s="10" t="n"/>
-      <c r="N131" s="10" t="inlineStr">
+      <c r="O131" s="10" t="n"/>
+      <c r="P131" s="10" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -38467,13 +38967,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L132" s="4" t="inlineStr">
+      <c r="N132" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M132" s="4" t="n"/>
-      <c r="N132" s="4" t="inlineStr">
+      <c r="O132" s="4" t="n"/>
+      <c r="P132" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -38529,13 +39029,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L133" s="4" t="inlineStr">
+      <c r="N133" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M133" s="4" t="n"/>
-      <c r="N133" s="4" t="inlineStr">
+      <c r="O133" s="4" t="n"/>
+      <c r="P133" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -38591,13 +39091,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L134" s="4" t="inlineStr">
+      <c r="N134" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M134" s="4" t="n"/>
-      <c r="N134" s="4" t="inlineStr">
+      <c r="O134" s="4" t="n"/>
+      <c r="P134" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -38653,13 +39153,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L135" s="4" t="inlineStr">
+      <c r="N135" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M135" s="4" t="n"/>
-      <c r="N135" s="4" t="inlineStr">
+      <c r="O135" s="4" t="n"/>
+      <c r="P135" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -38715,13 +39215,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L136" s="4" t="inlineStr">
+      <c r="N136" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M136" s="4" t="n"/>
-      <c r="N136" s="4" t="inlineStr">
+      <c r="O136" s="4" t="n"/>
+      <c r="P136" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -38777,13 +39277,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L137" s="4" t="inlineStr">
+      <c r="N137" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M137" s="4" t="n"/>
-      <c r="N137" s="4" t="inlineStr">
+      <c r="O137" s="4" t="n"/>
+      <c r="P137" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -38839,13 +39339,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L138" s="4" t="inlineStr">
+      <c r="N138" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M138" s="4" t="n"/>
-      <c r="N138" s="4" t="inlineStr">
+      <c r="O138" s="4" t="n"/>
+      <c r="P138" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -38901,13 +39401,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L139" s="4" t="inlineStr">
+      <c r="N139" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M139" s="4" t="n"/>
-      <c r="N139" s="4" t="inlineStr">
+      <c r="O139" s="4" t="n"/>
+      <c r="P139" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -38963,13 +39463,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L140" s="4" t="inlineStr">
+      <c r="N140" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M140" s="4" t="n"/>
-      <c r="N140" s="4" t="inlineStr">
+      <c r="O140" s="4" t="n"/>
+      <c r="P140" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -39025,13 +39525,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L141" s="4" t="inlineStr">
+      <c r="N141" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M141" s="4" t="n"/>
-      <c r="N141" s="4" t="inlineStr">
+      <c r="O141" s="4" t="n"/>
+      <c r="P141" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -39087,13 +39587,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L142" s="4" t="inlineStr">
+      <c r="N142" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M142" s="4" t="n"/>
-      <c r="N142" s="4" t="inlineStr">
+      <c r="O142" s="4" t="n"/>
+      <c r="P142" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -39149,13 +39649,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L143" s="4" t="inlineStr">
+      <c r="N143" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M143" s="4" t="n"/>
-      <c r="N143" s="4" t="inlineStr">
+      <c r="O143" s="4" t="n"/>
+      <c r="P143" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -39211,13 +39711,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L144" s="4" t="inlineStr">
+      <c r="N144" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M144" s="4" t="n"/>
-      <c r="N144" s="4" t="inlineStr">
+      <c r="O144" s="4" t="n"/>
+      <c r="P144" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -39273,13 +39773,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L145" s="4" t="inlineStr">
+      <c r="N145" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M145" s="4" t="n"/>
-      <c r="N145" s="4" t="inlineStr">
+      <c r="O145" s="4" t="n"/>
+      <c r="P145" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -39335,13 +39835,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L146" s="4" t="inlineStr">
+      <c r="N146" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M146" s="4" t="n"/>
-      <c r="N146" s="4" t="inlineStr">
+      <c r="O146" s="4" t="n"/>
+      <c r="P146" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -39397,13 +39897,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L147" s="4" t="inlineStr">
+      <c r="N147" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M147" s="4" t="n"/>
-      <c r="N147" s="4" t="inlineStr">
+      <c r="O147" s="4" t="n"/>
+      <c r="P147" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -39459,13 +39959,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L148" s="4" t="inlineStr">
+      <c r="N148" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M148" s="4" t="n"/>
-      <c r="N148" s="4" t="inlineStr">
+      <c r="O148" s="4" t="n"/>
+      <c r="P148" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -39521,13 +40021,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L149" s="4" t="inlineStr">
+      <c r="N149" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M149" s="4" t="n"/>
-      <c r="N149" s="4" t="inlineStr">
+      <c r="O149" s="4" t="n"/>
+      <c r="P149" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -39583,13 +40083,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L150" s="4" t="inlineStr">
+      <c r="N150" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M150" s="4" t="n"/>
-      <c r="N150" s="4" t="inlineStr">
+      <c r="O150" s="4" t="n"/>
+      <c r="P150" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -39645,13 +40145,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L151" s="4" t="inlineStr">
+      <c r="N151" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M151" s="4" t="n"/>
-      <c r="N151" s="4" t="inlineStr">
+      <c r="O151" s="4" t="n"/>
+      <c r="P151" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -39707,13 +40207,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L152" s="4" t="inlineStr">
+      <c r="N152" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M152" s="4" t="n"/>
-      <c r="N152" s="4" t="inlineStr">
+      <c r="O152" s="4" t="n"/>
+      <c r="P152" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -39769,13 +40269,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L153" s="4" t="inlineStr">
+      <c r="N153" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M153" s="4" t="n"/>
-      <c r="N153" s="4" t="inlineStr">
+      <c r="O153" s="4" t="n"/>
+      <c r="P153" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -39831,13 +40331,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L154" s="4" t="inlineStr">
+      <c r="N154" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M154" s="4" t="n"/>
-      <c r="N154" s="4" t="inlineStr">
+      <c r="O154" s="4" t="n"/>
+      <c r="P154" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -39893,13 +40393,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L155" s="4" t="inlineStr">
+      <c r="N155" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M155" s="4" t="n"/>
-      <c r="N155" s="4" t="inlineStr">
+      <c r="O155" s="4" t="n"/>
+      <c r="P155" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -39955,13 +40455,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L156" s="4" t="inlineStr">
+      <c r="N156" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M156" s="4" t="n"/>
-      <c r="N156" s="4" t="inlineStr">
+      <c r="O156" s="4" t="n"/>
+      <c r="P156" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -40017,13 +40517,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L157" s="4" t="inlineStr">
+      <c r="N157" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M157" s="4" t="n"/>
-      <c r="N157" s="4" t="inlineStr">
+      <c r="O157" s="4" t="n"/>
+      <c r="P157" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -40079,13 +40579,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L158" s="4" t="inlineStr">
+      <c r="N158" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M158" s="4" t="n"/>
-      <c r="N158" s="4" t="inlineStr">
+      <c r="O158" s="4" t="n"/>
+      <c r="P158" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -40141,13 +40641,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L159" s="4" t="inlineStr">
+      <c r="N159" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M159" s="4" t="n"/>
-      <c r="N159" s="4" t="inlineStr">
+      <c r="O159" s="4" t="n"/>
+      <c r="P159" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -40203,13 +40703,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L160" s="4" t="inlineStr">
+      <c r="N160" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M160" s="4" t="n"/>
-      <c r="N160" s="4" t="inlineStr">
+      <c r="O160" s="4" t="n"/>
+      <c r="P160" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -40265,13 +40765,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L161" s="4" t="inlineStr">
+      <c r="N161" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M161" s="4" t="n"/>
-      <c r="N161" s="4" t="inlineStr">
+      <c r="O161" s="4" t="n"/>
+      <c r="P161" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -40327,13 +40827,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L162" s="4" t="inlineStr">
+      <c r="N162" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M162" s="4" t="n"/>
-      <c r="N162" s="4" t="inlineStr">
+      <c r="O162" s="4" t="n"/>
+      <c r="P162" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -40389,13 +40889,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L163" s="4" t="inlineStr">
+      <c r="N163" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M163" s="4" t="n"/>
-      <c r="N163" s="4" t="inlineStr">
+      <c r="O163" s="4" t="n"/>
+      <c r="P163" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -40451,13 +40951,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L164" s="4" t="inlineStr">
+      <c r="N164" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M164" s="4" t="n"/>
-      <c r="N164" s="4" t="inlineStr">
+      <c r="O164" s="4" t="n"/>
+      <c r="P164" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -40513,13 +41013,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L165" s="4" t="inlineStr">
+      <c r="N165" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M165" s="4" t="n"/>
-      <c r="N165" s="4" t="inlineStr">
+      <c r="O165" s="4" t="n"/>
+      <c r="P165" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -40575,13 +41075,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L166" s="4" t="inlineStr">
+      <c r="N166" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M166" s="4" t="n"/>
-      <c r="N166" s="4" t="inlineStr">
+      <c r="O166" s="4" t="n"/>
+      <c r="P166" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -40637,13 +41137,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L167" s="4" t="inlineStr">
+      <c r="N167" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M167" s="4" t="n"/>
-      <c r="N167" s="4" t="inlineStr">
+      <c r="O167" s="4" t="n"/>
+      <c r="P167" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -40699,13 +41199,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L168" s="4" t="inlineStr">
+      <c r="N168" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M168" s="4" t="n"/>
-      <c r="N168" s="4" t="inlineStr">
+      <c r="O168" s="4" t="n"/>
+      <c r="P168" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -40761,13 +41261,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L169" s="4" t="inlineStr">
+      <c r="N169" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M169" s="4" t="n"/>
-      <c r="N169" s="4" t="inlineStr">
+      <c r="O169" s="4" t="n"/>
+      <c r="P169" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -40823,13 +41323,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L170" s="4" t="inlineStr">
+      <c r="N170" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M170" s="4" t="n"/>
-      <c r="N170" s="4" t="inlineStr">
+      <c r="O170" s="4" t="n"/>
+      <c r="P170" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -40885,13 +41385,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L171" s="4" t="inlineStr">
+      <c r="N171" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M171" s="4" t="n"/>
-      <c r="N171" s="4" t="inlineStr">
+      <c r="O171" s="4" t="n"/>
+      <c r="P171" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -40947,13 +41447,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L172" s="4" t="inlineStr">
+      <c r="N172" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M172" s="4" t="n"/>
-      <c r="N172" s="4" t="inlineStr">
+      <c r="O172" s="4" t="n"/>
+      <c r="P172" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -41009,13 +41509,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L173" s="4" t="inlineStr">
+      <c r="N173" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M173" s="4" t="n"/>
-      <c r="N173" s="4" t="inlineStr">
+      <c r="O173" s="4" t="n"/>
+      <c r="P173" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -41071,13 +41571,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L174" s="4" t="inlineStr">
+      <c r="N174" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M174" s="4" t="n"/>
-      <c r="N174" s="4" t="inlineStr">
+      <c r="O174" s="4" t="n"/>
+      <c r="P174" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -41133,13 +41633,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L175" s="4" t="inlineStr">
+      <c r="N175" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M175" s="4" t="n"/>
-      <c r="N175" s="4" t="inlineStr">
+      <c r="O175" s="4" t="n"/>
+      <c r="P175" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -41195,13 +41695,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L176" s="4" t="inlineStr">
+      <c r="N176" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M176" s="4" t="n"/>
-      <c r="N176" s="4" t="inlineStr">
+      <c r="O176" s="4" t="n"/>
+      <c r="P176" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -41257,13 +41757,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L177" s="4" t="inlineStr">
+      <c r="N177" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M177" s="4" t="n"/>
-      <c r="N177" s="4" t="inlineStr">
+      <c r="O177" s="4" t="n"/>
+      <c r="P177" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -41319,13 +41819,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L178" s="4" t="inlineStr">
+      <c r="N178" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M178" s="4" t="n"/>
-      <c r="N178" s="4" t="inlineStr">
+      <c r="O178" s="4" t="n"/>
+      <c r="P178" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -41381,13 +41881,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L179" s="4" t="inlineStr">
+      <c r="N179" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M179" s="4" t="n"/>
-      <c r="N179" s="4" t="inlineStr">
+      <c r="O179" s="4" t="n"/>
+      <c r="P179" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -41443,13 +41943,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L180" s="4" t="inlineStr">
+      <c r="N180" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M180" s="4" t="n"/>
-      <c r="N180" s="4" t="inlineStr">
+      <c r="O180" s="4" t="n"/>
+      <c r="P180" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -41505,13 +42005,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L181" s="4" t="inlineStr">
+      <c r="N181" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M181" s="4" t="n"/>
-      <c r="N181" s="4" t="inlineStr">
+      <c r="O181" s="4" t="n"/>
+      <c r="P181" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -41567,13 +42067,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L182" s="4" t="inlineStr">
+      <c r="N182" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M182" s="4" t="n"/>
-      <c r="N182" s="4" t="inlineStr">
+      <c r="O182" s="4" t="n"/>
+      <c r="P182" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -41629,13 +42129,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L183" s="4" t="inlineStr">
+      <c r="N183" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M183" s="4" t="n"/>
-      <c r="N183" s="4" t="inlineStr">
+      <c r="O183" s="4" t="n"/>
+      <c r="P183" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -41691,13 +42191,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L184" s="4" t="inlineStr">
+      <c r="N184" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M184" s="4" t="n"/>
-      <c r="N184" s="4" t="inlineStr">
+      <c r="O184" s="4" t="n"/>
+      <c r="P184" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -41753,13 +42253,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L185" s="4" t="inlineStr">
+      <c r="N185" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M185" s="4" t="n"/>
-      <c r="N185" s="4" t="inlineStr">
+      <c r="O185" s="4" t="n"/>
+      <c r="P185" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -41815,13 +42315,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L186" s="4" t="inlineStr">
+      <c r="N186" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M186" s="4" t="n"/>
-      <c r="N186" s="4" t="inlineStr">
+      <c r="O186" s="4" t="n"/>
+      <c r="P186" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -41877,13 +42377,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L187" s="4" t="inlineStr">
+      <c r="N187" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M187" s="4" t="n"/>
-      <c r="N187" s="4" t="inlineStr">
+      <c r="O187" s="4" t="n"/>
+      <c r="P187" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -41939,13 +42439,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L188" s="4" t="inlineStr">
+      <c r="N188" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M188" s="4" t="n"/>
-      <c r="N188" s="4" t="inlineStr">
+      <c r="O188" s="4" t="n"/>
+      <c r="P188" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -42001,13 +42501,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L189" s="4" t="inlineStr">
+      <c r="N189" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M189" s="4" t="n"/>
-      <c r="N189" s="4" t="inlineStr">
+      <c r="O189" s="4" t="n"/>
+      <c r="P189" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -42063,13 +42563,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L190" s="4" t="inlineStr">
+      <c r="N190" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M190" s="4" t="n"/>
-      <c r="N190" s="4" t="inlineStr">
+      <c r="O190" s="4" t="n"/>
+      <c r="P190" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -42125,13 +42625,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L191" s="4" t="inlineStr">
+      <c r="N191" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M191" s="4" t="n"/>
-      <c r="N191" s="4" t="inlineStr">
+      <c r="O191" s="4" t="n"/>
+      <c r="P191" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -42187,13 +42687,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L192" s="4" t="inlineStr">
+      <c r="N192" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M192" s="4" t="n"/>
-      <c r="N192" s="4" t="inlineStr">
+      <c r="O192" s="4" t="n"/>
+      <c r="P192" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -42249,13 +42749,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L193" s="4" t="inlineStr">
+      <c r="N193" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M193" s="4" t="n"/>
-      <c r="N193" s="4" t="inlineStr">
+      <c r="O193" s="4" t="n"/>
+      <c r="P193" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -42311,13 +42811,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L194" s="4" t="inlineStr">
+      <c r="N194" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M194" s="4" t="n"/>
-      <c r="N194" s="4" t="inlineStr">
+      <c r="O194" s="4" t="n"/>
+      <c r="P194" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -42373,13 +42873,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L195" s="4" t="inlineStr">
+      <c r="N195" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M195" s="4" t="n"/>
-      <c r="N195" s="4" t="inlineStr">
+      <c r="O195" s="4" t="n"/>
+      <c r="P195" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -42435,13 +42935,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L196" s="4" t="inlineStr">
+      <c r="N196" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M196" s="4" t="n"/>
-      <c r="N196" s="4" t="inlineStr">
+      <c r="O196" s="4" t="n"/>
+      <c r="P196" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -42497,13 +42997,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L197" s="4" t="inlineStr">
+      <c r="N197" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M197" s="4" t="n"/>
-      <c r="N197" s="4" t="inlineStr">
+      <c r="O197" s="4" t="n"/>
+      <c r="P197" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -42559,13 +43059,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L198" s="4" t="inlineStr">
+      <c r="N198" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M198" s="4" t="n"/>
-      <c r="N198" s="4" t="inlineStr">
+      <c r="O198" s="4" t="n"/>
+      <c r="P198" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -42621,13 +43121,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L199" s="4" t="inlineStr">
+      <c r="N199" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M199" s="4" t="n"/>
-      <c r="N199" s="4" t="inlineStr">
+      <c r="O199" s="4" t="n"/>
+      <c r="P199" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -42683,13 +43183,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L200" s="4" t="inlineStr">
+      <c r="N200" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M200" s="4" t="n"/>
-      <c r="N200" s="4" t="inlineStr">
+      <c r="O200" s="4" t="n"/>
+      <c r="P200" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -42745,13 +43245,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L201" s="4" t="inlineStr">
+      <c r="N201" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M201" s="4" t="n"/>
-      <c r="N201" s="4" t="inlineStr">
+      <c r="O201" s="4" t="n"/>
+      <c r="P201" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -42807,13 +43307,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L202" s="4" t="inlineStr">
+      <c r="N202" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M202" s="4" t="n"/>
-      <c r="N202" s="4" t="inlineStr">
+      <c r="O202" s="4" t="n"/>
+      <c r="P202" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -42869,13 +43369,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L203" s="4" t="inlineStr">
+      <c r="N203" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M203" s="4" t="n"/>
-      <c r="N203" s="4" t="inlineStr">
+      <c r="O203" s="4" t="n"/>
+      <c r="P203" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -42931,13 +43431,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L204" s="4" t="inlineStr">
+      <c r="N204" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M204" s="4" t="n"/>
-      <c r="N204" s="4" t="inlineStr">
+      <c r="O204" s="4" t="n"/>
+      <c r="P204" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -42993,13 +43493,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L205" s="4" t="inlineStr">
+      <c r="N205" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M205" s="4" t="n"/>
-      <c r="N205" s="4" t="inlineStr">
+      <c r="O205" s="4" t="n"/>
+      <c r="P205" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -43055,13 +43555,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L206" s="4" t="inlineStr">
+      <c r="N206" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M206" s="4" t="n"/>
-      <c r="N206" s="4" t="inlineStr">
+      <c r="O206" s="4" t="n"/>
+      <c r="P206" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -43117,13 +43617,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L207" s="4" t="inlineStr">
+      <c r="N207" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M207" s="4" t="n"/>
-      <c r="N207" s="4" t="inlineStr">
+      <c r="O207" s="4" t="n"/>
+      <c r="P207" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -43179,13 +43679,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L208" s="4" t="inlineStr">
+      <c r="N208" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M208" s="4" t="n"/>
-      <c r="N208" s="4" t="inlineStr">
+      <c r="O208" s="4" t="n"/>
+      <c r="P208" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -43241,13 +43741,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L209" s="4" t="inlineStr">
+      <c r="N209" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M209" s="4" t="n"/>
-      <c r="N209" s="4" t="inlineStr">
+      <c r="O209" s="4" t="n"/>
+      <c r="P209" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -43303,13 +43803,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L210" s="4" t="inlineStr">
+      <c r="N210" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M210" s="4" t="n"/>
-      <c r="N210" s="4" t="inlineStr">
+      <c r="O210" s="4" t="n"/>
+      <c r="P210" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -43365,13 +43865,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L211" s="4" t="inlineStr">
+      <c r="N211" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M211" s="4" t="n"/>
-      <c r="N211" s="4" t="inlineStr">
+      <c r="O211" s="4" t="n"/>
+      <c r="P211" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -43427,13 +43927,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L212" s="4" t="inlineStr">
+      <c r="N212" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M212" s="4" t="n"/>
-      <c r="N212" s="4" t="inlineStr">
+      <c r="O212" s="4" t="n"/>
+      <c r="P212" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -43489,13 +43989,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L213" s="4" t="inlineStr">
+      <c r="N213" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M213" s="4" t="n"/>
-      <c r="N213" s="4" t="inlineStr">
+      <c r="O213" s="4" t="n"/>
+      <c r="P213" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -43551,13 +44051,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L214" s="4" t="inlineStr">
+      <c r="N214" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M214" s="4" t="n"/>
-      <c r="N214" s="4" t="inlineStr">
+      <c r="O214" s="4" t="n"/>
+      <c r="P214" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -43613,13 +44113,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L215" s="4" t="inlineStr">
+      <c r="N215" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M215" s="4" t="n"/>
-      <c r="N215" s="4" t="inlineStr">
+      <c r="O215" s="4" t="n"/>
+      <c r="P215" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -43675,13 +44175,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L216" s="4" t="inlineStr">
+      <c r="N216" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M216" s="4" t="n"/>
-      <c r="N216" s="4" t="inlineStr">
+      <c r="O216" s="4" t="n"/>
+      <c r="P216" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -43737,13 +44237,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L217" s="4" t="inlineStr">
+      <c r="N217" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M217" s="4" t="n"/>
-      <c r="N217" s="4" t="inlineStr">
+      <c r="O217" s="4" t="n"/>
+      <c r="P217" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -43799,13 +44299,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L218" s="4" t="inlineStr">
+      <c r="N218" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M218" s="4" t="n"/>
-      <c r="N218" s="4" t="inlineStr">
+      <c r="O218" s="4" t="n"/>
+      <c r="P218" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -43861,13 +44361,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L219" s="4" t="inlineStr">
+      <c r="N219" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M219" s="4" t="n"/>
-      <c r="N219" s="4" t="inlineStr">
+      <c r="O219" s="4" t="n"/>
+      <c r="P219" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -43923,13 +44423,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L220" s="4" t="inlineStr">
+      <c r="N220" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M220" s="4" t="n"/>
-      <c r="N220" s="4" t="inlineStr">
+      <c r="O220" s="4" t="n"/>
+      <c r="P220" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -43985,13 +44485,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L221" s="4" t="inlineStr">
+      <c r="N221" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M221" s="4" t="n"/>
-      <c r="N221" s="4" t="inlineStr">
+      <c r="O221" s="4" t="n"/>
+      <c r="P221" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -44047,13 +44547,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L222" s="4" t="inlineStr">
+      <c r="N222" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M222" s="4" t="n"/>
-      <c r="N222" s="4" t="inlineStr">
+      <c r="O222" s="4" t="n"/>
+      <c r="P222" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -44109,13 +44609,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L223" s="4" t="inlineStr">
+      <c r="N223" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M223" s="4" t="n"/>
-      <c r="N223" s="4" t="inlineStr">
+      <c r="O223" s="4" t="n"/>
+      <c r="P223" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -44171,13 +44671,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L224" s="4" t="inlineStr">
+      <c r="N224" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M224" s="4" t="n"/>
-      <c r="N224" s="4" t="inlineStr">
+      <c r="O224" s="4" t="n"/>
+      <c r="P224" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -44233,13 +44733,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L225" s="4" t="inlineStr">
+      <c r="N225" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M225" s="4" t="n"/>
-      <c r="N225" s="4" t="inlineStr">
+      <c r="O225" s="4" t="n"/>
+      <c r="P225" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -44295,13 +44795,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L226" s="4" t="inlineStr">
+      <c r="N226" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M226" s="4" t="n"/>
-      <c r="N226" s="4" t="inlineStr">
+      <c r="O226" s="4" t="n"/>
+      <c r="P226" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -44357,13 +44857,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L227" s="4" t="inlineStr">
+      <c r="N227" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M227" s="4" t="n"/>
-      <c r="N227" s="4" t="inlineStr">
+      <c r="O227" s="4" t="n"/>
+      <c r="P227" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -44419,13 +44919,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L228" s="4" t="inlineStr">
+      <c r="N228" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M228" s="4" t="n"/>
-      <c r="N228" s="4" t="inlineStr">
+      <c r="O228" s="4" t="n"/>
+      <c r="P228" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -44481,13 +44981,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L229" s="4" t="inlineStr">
+      <c r="N229" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M229" s="4" t="n"/>
-      <c r="N229" s="4" t="inlineStr">
+      <c r="O229" s="4" t="n"/>
+      <c r="P229" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -44543,13 +45043,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L230" s="4" t="inlineStr">
+      <c r="N230" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M230" s="4" t="n"/>
-      <c r="N230" s="4" t="inlineStr">
+      <c r="O230" s="4" t="n"/>
+      <c r="P230" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -44605,13 +45105,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L231" s="4" t="inlineStr">
+      <c r="N231" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M231" s="4" t="n"/>
-      <c r="N231" s="4" t="inlineStr">
+      <c r="O231" s="4" t="n"/>
+      <c r="P231" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -44667,13 +45167,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L232" s="4" t="inlineStr">
+      <c r="N232" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M232" s="4" t="n"/>
-      <c r="N232" s="4" t="inlineStr">
+      <c r="O232" s="4" t="n"/>
+      <c r="P232" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -44729,13 +45229,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L233" s="4" t="inlineStr">
+      <c r="N233" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M233" s="4" t="n"/>
-      <c r="N233" s="4" t="inlineStr">
+      <c r="O233" s="4" t="n"/>
+      <c r="P233" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -44791,13 +45291,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L234" s="4" t="inlineStr">
+      <c r="N234" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M234" s="4" t="n"/>
-      <c r="N234" s="4" t="inlineStr">
+      <c r="O234" s="4" t="n"/>
+      <c r="P234" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -44853,13 +45353,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L235" s="4" t="inlineStr">
+      <c r="N235" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M235" s="4" t="n"/>
-      <c r="N235" s="4" t="inlineStr">
+      <c r="O235" s="4" t="n"/>
+      <c r="P235" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -44915,13 +45415,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L236" s="4" t="inlineStr">
+      <c r="N236" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M236" s="4" t="n"/>
-      <c r="N236" s="4" t="inlineStr">
+      <c r="O236" s="4" t="n"/>
+      <c r="P236" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -44977,13 +45477,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L237" s="4" t="inlineStr">
+      <c r="N237" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M237" s="4" t="n"/>
-      <c r="N237" s="4" t="inlineStr">
+      <c r="O237" s="4" t="n"/>
+      <c r="P237" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -45039,13 +45539,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L238" s="4" t="inlineStr">
+      <c r="N238" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M238" s="4" t="n"/>
-      <c r="N238" s="4" t="inlineStr">
+      <c r="O238" s="4" t="n"/>
+      <c r="P238" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -45101,13 +45601,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L239" s="4" t="inlineStr">
+      <c r="N239" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M239" s="4" t="n"/>
-      <c r="N239" s="4" t="inlineStr">
+      <c r="O239" s="4" t="n"/>
+      <c r="P239" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -45163,13 +45663,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L240" s="4" t="inlineStr">
+      <c r="N240" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M240" s="4" t="n"/>
-      <c r="N240" s="4" t="inlineStr">
+      <c r="O240" s="4" t="n"/>
+      <c r="P240" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -45225,13 +45725,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L241" s="4" t="inlineStr">
+      <c r="N241" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M241" s="4" t="n"/>
-      <c r="N241" s="4" t="inlineStr">
+      <c r="O241" s="4" t="n"/>
+      <c r="P241" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -45287,13 +45787,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L242" s="4" t="inlineStr">
+      <c r="N242" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M242" s="4" t="n"/>
-      <c r="N242" s="4" t="inlineStr">
+      <c r="O242" s="4" t="n"/>
+      <c r="P242" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -45349,13 +45849,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L243" s="4" t="inlineStr">
+      <c r="N243" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M243" s="4" t="n"/>
-      <c r="N243" s="4" t="inlineStr">
+      <c r="O243" s="4" t="n"/>
+      <c r="P243" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -45411,13 +45911,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L244" s="4" t="inlineStr">
+      <c r="N244" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M244" s="4" t="n"/>
-      <c r="N244" s="4" t="inlineStr">
+      <c r="O244" s="4" t="n"/>
+      <c r="P244" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -45473,13 +45973,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L245" s="4" t="inlineStr">
+      <c r="N245" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M245" s="4" t="n"/>
-      <c r="N245" s="4" t="inlineStr">
+      <c r="O245" s="4" t="n"/>
+      <c r="P245" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -45535,13 +46035,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L246" s="4" t="inlineStr">
+      <c r="N246" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M246" s="4" t="n"/>
-      <c r="N246" s="4" t="inlineStr">
+      <c r="O246" s="4" t="n"/>
+      <c r="P246" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -45597,13 +46097,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L247" s="4" t="inlineStr">
+      <c r="N247" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M247" s="4" t="n"/>
-      <c r="N247" s="4" t="inlineStr">
+      <c r="O247" s="4" t="n"/>
+      <c r="P247" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -45659,13 +46159,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L248" s="4" t="inlineStr">
+      <c r="N248" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M248" s="4" t="n"/>
-      <c r="N248" s="4" t="inlineStr">
+      <c r="O248" s="4" t="n"/>
+      <c r="P248" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -45721,13 +46221,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L249" s="4" t="inlineStr">
+      <c r="N249" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M249" s="4" t="n"/>
-      <c r="N249" s="4" t="inlineStr">
+      <c r="O249" s="4" t="n"/>
+      <c r="P249" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -45783,13 +46283,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L250" s="4" t="inlineStr">
+      <c r="N250" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M250" s="4" t="n"/>
-      <c r="N250" s="4" t="inlineStr">
+      <c r="O250" s="4" t="n"/>
+      <c r="P250" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -45845,13 +46345,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L251" s="4" t="inlineStr">
+      <c r="N251" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M251" s="4" t="n"/>
-      <c r="N251" s="4" t="inlineStr">
+      <c r="O251" s="4" t="n"/>
+      <c r="P251" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -45907,13 +46407,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L252" s="4" t="inlineStr">
+      <c r="N252" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M252" s="4" t="n"/>
-      <c r="N252" s="4" t="inlineStr">
+      <c r="O252" s="4" t="n"/>
+      <c r="P252" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -45969,13 +46469,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L253" s="4" t="inlineStr">
+      <c r="N253" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M253" s="4" t="n"/>
-      <c r="N253" s="4" t="inlineStr">
+      <c r="O253" s="4" t="n"/>
+      <c r="P253" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -46031,13 +46531,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L254" s="4" t="inlineStr">
+      <c r="N254" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M254" s="4" t="n"/>
-      <c r="N254" s="4" t="inlineStr">
+      <c r="O254" s="4" t="n"/>
+      <c r="P254" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -46093,13 +46593,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L255" s="4" t="inlineStr">
+      <c r="N255" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M255" s="4" t="n"/>
-      <c r="N255" s="4" t="inlineStr">
+      <c r="O255" s="4" t="n"/>
+      <c r="P255" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -46155,13 +46655,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L256" s="4" t="inlineStr">
+      <c r="N256" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M256" s="4" t="n"/>
-      <c r="N256" s="4" t="inlineStr">
+      <c r="O256" s="4" t="n"/>
+      <c r="P256" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -46217,13 +46717,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L257" s="4" t="inlineStr">
+      <c r="N257" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M257" s="4" t="n"/>
-      <c r="N257" s="4" t="inlineStr">
+      <c r="O257" s="4" t="n"/>
+      <c r="P257" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -46279,13 +46779,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L258" s="4" t="inlineStr">
+      <c r="N258" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M258" s="4" t="n"/>
-      <c r="N258" s="4" t="inlineStr">
+      <c r="O258" s="4" t="n"/>
+      <c r="P258" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -46341,13 +46841,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L259" s="4" t="inlineStr">
+      <c r="N259" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M259" s="4" t="n"/>
-      <c r="N259" s="4" t="inlineStr">
+      <c r="O259" s="4" t="n"/>
+      <c r="P259" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -46403,13 +46903,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L260" s="4" t="inlineStr">
+      <c r="N260" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M260" s="4" t="n"/>
-      <c r="N260" s="4" t="inlineStr">
+      <c r="O260" s="4" t="n"/>
+      <c r="P260" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -46465,13 +46965,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L261" s="4" t="inlineStr">
+      <c r="N261" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M261" s="4" t="n"/>
-      <c r="N261" s="4" t="inlineStr">
+      <c r="O261" s="4" t="n"/>
+      <c r="P261" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -46527,13 +47027,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L262" s="4" t="inlineStr">
+      <c r="N262" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M262" s="4" t="n"/>
-      <c r="N262" s="4" t="inlineStr">
+      <c r="O262" s="4" t="n"/>
+      <c r="P262" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -46589,13 +47089,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L263" s="4" t="inlineStr">
+      <c r="N263" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M263" s="4" t="n"/>
-      <c r="N263" s="4" t="inlineStr">
+      <c r="O263" s="4" t="n"/>
+      <c r="P263" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -46651,13 +47151,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L264" s="4" t="inlineStr">
+      <c r="N264" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M264" s="4" t="n"/>
-      <c r="N264" s="4" t="inlineStr">
+      <c r="O264" s="4" t="n"/>
+      <c r="P264" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -46713,13 +47213,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L265" s="4" t="inlineStr">
+      <c r="N265" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M265" s="4" t="n"/>
-      <c r="N265" s="4" t="inlineStr">
+      <c r="O265" s="4" t="n"/>
+      <c r="P265" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -46775,13 +47275,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L266" s="4" t="inlineStr">
+      <c r="N266" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M266" s="4" t="n"/>
-      <c r="N266" s="4" t="inlineStr">
+      <c r="O266" s="4" t="n"/>
+      <c r="P266" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -46837,13 +47337,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L267" s="4" t="inlineStr">
+      <c r="N267" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M267" s="4" t="n"/>
-      <c r="N267" s="4" t="inlineStr">
+      <c r="O267" s="4" t="n"/>
+      <c r="P267" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -46899,13 +47399,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L268" s="4" t="inlineStr">
+      <c r="N268" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M268" s="4" t="n"/>
-      <c r="N268" s="4" t="inlineStr">
+      <c r="O268" s="4" t="n"/>
+      <c r="P268" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -46961,13 +47461,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L269" s="4" t="inlineStr">
+      <c r="N269" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M269" s="4" t="n"/>
-      <c r="N269" s="4" t="inlineStr">
+      <c r="O269" s="4" t="n"/>
+      <c r="P269" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -47023,13 +47523,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L270" s="4" t="inlineStr">
+      <c r="N270" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M270" s="4" t="n"/>
-      <c r="N270" s="4" t="inlineStr">
+      <c r="O270" s="4" t="n"/>
+      <c r="P270" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -47085,13 +47585,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L271" s="4" t="inlineStr">
+      <c r="N271" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M271" s="4" t="n"/>
-      <c r="N271" s="4" t="inlineStr">
+      <c r="O271" s="4" t="n"/>
+      <c r="P271" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -47147,13 +47647,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L272" s="4" t="inlineStr">
+      <c r="N272" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M272" s="4" t="n"/>
-      <c r="N272" s="4" t="inlineStr">
+      <c r="O272" s="4" t="n"/>
+      <c r="P272" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -47209,13 +47709,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L273" s="4" t="inlineStr">
+      <c r="N273" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M273" s="4" t="n"/>
-      <c r="N273" s="4" t="inlineStr">
+      <c r="O273" s="4" t="n"/>
+      <c r="P273" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -47271,13 +47771,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L274" s="4" t="inlineStr">
+      <c r="N274" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M274" s="4" t="n"/>
-      <c r="N274" s="4" t="inlineStr">
+      <c r="O274" s="4" t="n"/>
+      <c r="P274" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -47333,13 +47833,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L275" s="4" t="inlineStr">
+      <c r="N275" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M275" s="4" t="n"/>
-      <c r="N275" s="4" t="inlineStr">
+      <c r="O275" s="4" t="n"/>
+      <c r="P275" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -47395,13 +47895,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L276" s="4" t="inlineStr">
+      <c r="N276" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M276" s="4" t="n"/>
-      <c r="N276" s="4" t="inlineStr">
+      <c r="O276" s="4" t="n"/>
+      <c r="P276" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -47457,13 +47957,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L277" s="4" t="inlineStr">
+      <c r="N277" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M277" s="4" t="n"/>
-      <c r="N277" s="4" t="inlineStr">
+      <c r="O277" s="4" t="n"/>
+      <c r="P277" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -47519,13 +48019,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L278" s="4" t="inlineStr">
+      <c r="N278" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M278" s="4" t="n"/>
-      <c r="N278" s="4" t="inlineStr">
+      <c r="O278" s="4" t="n"/>
+      <c r="P278" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -47581,13 +48081,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L279" s="4" t="inlineStr">
+      <c r="N279" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M279" s="4" t="n"/>
-      <c r="N279" s="4" t="inlineStr">
+      <c r="O279" s="4" t="n"/>
+      <c r="P279" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -47643,13 +48143,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L280" s="4" t="inlineStr">
+      <c r="N280" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M280" s="4" t="n"/>
-      <c r="N280" s="4" t="inlineStr">
+      <c r="O280" s="4" t="n"/>
+      <c r="P280" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -47705,13 +48205,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L281" s="4" t="inlineStr">
+      <c r="N281" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M281" s="4" t="n"/>
-      <c r="N281" s="4" t="inlineStr">
+      <c r="O281" s="4" t="n"/>
+      <c r="P281" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -47767,13 +48267,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L282" s="4" t="inlineStr">
+      <c r="N282" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M282" s="4" t="n"/>
-      <c r="N282" s="4" t="inlineStr">
+      <c r="O282" s="4" t="n"/>
+      <c r="P282" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -47829,13 +48329,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L283" s="4" t="inlineStr">
+      <c r="N283" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M283" s="4" t="n"/>
-      <c r="N283" s="4" t="inlineStr">
+      <c r="O283" s="4" t="n"/>
+      <c r="P283" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -47891,13 +48391,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L284" s="4" t="inlineStr">
+      <c r="N284" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M284" s="4" t="n"/>
-      <c r="N284" s="4" t="inlineStr">
+      <c r="O284" s="4" t="n"/>
+      <c r="P284" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -47953,13 +48453,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L285" s="4" t="inlineStr">
+      <c r="N285" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE103</t>
         </is>
       </c>
-      <c r="M285" s="4" t="n"/>
-      <c r="N285" s="4" t="inlineStr">
+      <c r="O285" s="4" t="n"/>
+      <c r="P285" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -48015,13 +48515,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L286" s="4" t="inlineStr">
+      <c r="N286" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M286" s="4" t="n"/>
-      <c r="N286" s="4" t="inlineStr">
+      <c r="O286" s="4" t="n"/>
+      <c r="P286" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -48077,13 +48577,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L287" s="4" t="inlineStr">
+      <c r="N287" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE104</t>
         </is>
       </c>
-      <c r="M287" s="4" t="n"/>
-      <c r="N287" s="4" t="inlineStr">
+      <c r="O287" s="4" t="n"/>
+      <c r="P287" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -48139,13 +48639,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L288" s="4" t="inlineStr">
+      <c r="N288" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M288" s="4" t="n"/>
-      <c r="N288" s="4" t="inlineStr">
+      <c r="O288" s="4" t="n"/>
+      <c r="P288" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -48201,13 +48701,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L289" s="4" t="inlineStr">
+      <c r="N289" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE106</t>
         </is>
       </c>
-      <c r="M289" s="4" t="n"/>
-      <c r="N289" s="4" t="inlineStr">
+      <c r="O289" s="4" t="n"/>
+      <c r="P289" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -48263,13 +48763,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L290" s="4" t="inlineStr">
+      <c r="N290" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M290" s="4" t="n"/>
-      <c r="N290" s="4" t="inlineStr">
+      <c r="O290" s="4" t="n"/>
+      <c r="P290" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -48325,13 +48825,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L291" s="4" t="inlineStr">
+      <c r="N291" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M291" s="4" t="n"/>
-      <c r="N291" s="4" t="inlineStr">
+      <c r="O291" s="4" t="n"/>
+      <c r="P291" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -48387,13 +48887,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L292" s="4" t="inlineStr">
+      <c r="N292" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M292" s="4" t="n"/>
-      <c r="N292" s="4" t="inlineStr">
+      <c r="O292" s="4" t="n"/>
+      <c r="P292" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -48449,13 +48949,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L293" s="4" t="inlineStr">
+      <c r="N293" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M293" s="4" t="n"/>
-      <c r="N293" s="4" t="inlineStr">
+      <c r="O293" s="4" t="n"/>
+      <c r="P293" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -48511,13 +49011,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L294" s="4" t="inlineStr">
+      <c r="N294" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M294" s="4" t="n"/>
-      <c r="N294" s="4" t="inlineStr">
+      <c r="O294" s="4" t="n"/>
+      <c r="P294" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -48573,13 +49073,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L295" s="4" t="inlineStr">
+      <c r="N295" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M295" s="4" t="n"/>
-      <c r="N295" s="4" t="inlineStr">
+      <c r="O295" s="4" t="n"/>
+      <c r="P295" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -48635,13 +49135,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L296" s="4" t="inlineStr">
+      <c r="N296" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE100</t>
         </is>
       </c>
-      <c r="M296" s="4" t="n"/>
-      <c r="N296" s="4" t="inlineStr">
+      <c r="O296" s="4" t="n"/>
+      <c r="P296" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -48697,13 +49197,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L297" s="4" t="inlineStr">
+      <c r="N297" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M297" s="4" t="n"/>
-      <c r="N297" s="4" t="inlineStr">
+      <c r="O297" s="4" t="n"/>
+      <c r="P297" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -48759,13 +49259,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L298" s="4" t="inlineStr">
+      <c r="N298" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M298" s="4" t="n"/>
-      <c r="N298" s="4" t="inlineStr">
+      <c r="O298" s="4" t="n"/>
+      <c r="P298" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -48821,13 +49321,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L299" s="4" t="inlineStr">
+      <c r="N299" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M299" s="4" t="n"/>
-      <c r="N299" s="4" t="inlineStr">
+      <c r="O299" s="4" t="n"/>
+      <c r="P299" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -48883,13 +49383,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L300" s="4" t="inlineStr">
+      <c r="N300" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M300" s="4" t="n"/>
-      <c r="N300" s="4" t="inlineStr">
+      <c r="O300" s="4" t="n"/>
+      <c r="P300" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -48945,13 +49445,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L301" s="4" t="inlineStr">
+      <c r="N301" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M301" s="4" t="n"/>
-      <c r="N301" s="4" t="inlineStr">
+      <c r="O301" s="4" t="n"/>
+      <c r="P301" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -49007,13 +49507,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L302" s="4" t="inlineStr">
+      <c r="N302" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M302" s="4" t="n"/>
-      <c r="N302" s="4" t="inlineStr">
+      <c r="O302" s="4" t="n"/>
+      <c r="P302" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -49069,13 +49569,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L303" s="4" t="inlineStr">
+      <c r="N303" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M303" s="4" t="n"/>
-      <c r="N303" s="4" t="inlineStr">
+      <c r="O303" s="4" t="n"/>
+      <c r="P303" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -49131,13 +49631,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L304" s="4" t="inlineStr">
+      <c r="N304" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M304" s="4" t="n"/>
-      <c r="N304" s="4" t="inlineStr">
+      <c r="O304" s="4" t="n"/>
+      <c r="P304" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -49193,13 +49693,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L305" s="4" t="inlineStr">
+      <c r="N305" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE101</t>
         </is>
       </c>
-      <c r="M305" s="4" t="n"/>
-      <c r="N305" s="4" t="inlineStr">
+      <c r="O305" s="4" t="n"/>
+      <c r="P305" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -49253,13 +49753,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L306" s="4" t="inlineStr">
+      <c r="N306" s="4" t="inlineStr">
         <is>
           <t>CMP-SAE108</t>
         </is>
       </c>
-      <c r="M306" s="4" t="n"/>
-      <c r="N306" s="4" t="inlineStr">
+      <c r="O306" s="4" t="n"/>
+      <c r="P306" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -49315,13 +49815,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L307" s="4" t="inlineStr">
+      <c r="N307" s="4" t="inlineStr">
         <is>
           <t>CMP-CHQ100</t>
         </is>
       </c>
-      <c r="M307" s="4" t="n"/>
-      <c r="N307" s="4" t="inlineStr">
+      <c r="O307" s="4" t="n"/>
+      <c r="P307" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -49377,13 +49877,13 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="L308" s="4" t="inlineStr">
+      <c r="N308" s="4" t="inlineStr">
         <is>
           <t>CMP-CrMo41</t>
         </is>
       </c>
-      <c r="M308" s="4" t="n"/>
-      <c r="N308" s="4" t="inlineStr">
+      <c r="O308" s="4" t="n"/>
+      <c r="P308" s="4" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>

--- a/APS_BF_SMS_RM.xlsx
+++ b/APS_BF_SMS_RM.xlsx
@@ -33112,7 +33112,7 @@
       </c>
       <c r="O39" s="11" t="inlineStr">
         <is>
-          <t>PO-0002</t>
+          <t>PO-0001</t>
         </is>
       </c>
       <c r="P39" s="11" t="inlineStr">
@@ -33178,7 +33178,7 @@
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
-          <t>PO-0005</t>
+          <t>PO-0002</t>
         </is>
       </c>
       <c r="P40" s="11" t="inlineStr">
@@ -33896,7 +33896,7 @@
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>PO-0009</t>
+          <t>PO-0003</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">

--- a/APS_BF_SMS_RM.xlsx
+++ b/APS_BF_SMS_RM.xlsx
@@ -31175,13 +31175,17 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE103</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>PO-0028</t>
+        </is>
+      </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -32005,13 +32009,17 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE106</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>PO-0029</t>
+        </is>
+      </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -32199,13 +32207,17 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE108</t>
-        </is>
-      </c>
-      <c r="O25" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>PO-0030</t>
+        </is>
+      </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -32389,13 +32401,17 @@
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE100</t>
-        </is>
-      </c>
-      <c r="O28" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>PO-0027</t>
+        </is>
+      </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -33112,7 +33128,7 @@
       </c>
       <c r="O39" s="11" t="inlineStr">
         <is>
-          <t>PO-0001</t>
+          <t>PO-0002</t>
         </is>
       </c>
       <c r="P39" s="11" t="inlineStr">
@@ -33178,7 +33194,7 @@
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
-          <t>PO-0002</t>
+          <t>PO-0005</t>
         </is>
       </c>
       <c r="P40" s="11" t="inlineStr">
@@ -33503,13 +33519,17 @@
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE103</t>
-        </is>
-      </c>
-      <c r="O45" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>PO-0028</t>
+        </is>
+      </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -33896,7 +33916,7 @@
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>PO-0003</t>
+          <t>PO-0009</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">

--- a/APS_BF_SMS_RM.xlsx
+++ b/APS_BF_SMS_RM.xlsx
@@ -8549,7 +8549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18" customWidth="1" style="35" min="1" max="4"/>
@@ -8916,6 +8916,23 @@
       <c r="D18" t="inlineStr">
         <is>
           <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>REQ-1775732423862</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FG-WR-SAE1018-100</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -30845,17 +30862,17 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE101</t>
+          <t>APS_RELEASED</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>CMP-002</t>
+          <t>PO-0025</t>
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -30911,17 +30928,17 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE108</t>
+          <t>APS_RELEASED</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>CMP-001</t>
+          <t>PO-0036</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -31180,7 +31197,7 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>PO-0028</t>
+          <t>PO-0027</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
@@ -31757,13 +31774,17 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE103</t>
-        </is>
-      </c>
-      <c r="O18" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>PO-0027</t>
+        </is>
+      </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -31947,13 +31968,17 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>CMP-CrMo41</t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>PO-0034</t>
+        </is>
+      </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -32014,7 +32039,7 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>PO-0029</t>
+          <t>PO-0032</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr">
@@ -32212,7 +32237,7 @@
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>PO-0030</t>
+          <t>PO-0033</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
@@ -32406,7 +32431,7 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>PO-0027</t>
+          <t>PO-0030</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
@@ -32533,13 +32558,17 @@
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE101</t>
-        </is>
-      </c>
-      <c r="O30" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>PO-0035</t>
+        </is>
+      </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -32996,7 +33025,7 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>PO-0026</t>
+          <t>PO-0029</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
@@ -33062,7 +33091,7 @@
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>PO-0025</t>
+          <t>PO-0028</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
@@ -33524,7 +33553,7 @@
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>PO-0028</t>
+          <t>PO-0031</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
@@ -33585,13 +33614,17 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE103</t>
-        </is>
-      </c>
-      <c r="O46" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>PO-0026</t>
+        </is>
+      </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -34695,13 +34728,17 @@
       </c>
       <c r="N63" s="10" t="inlineStr">
         <is>
-          <t>CMP-SAE101</t>
-        </is>
-      </c>
-      <c r="O63" s="10" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O63" s="10" t="inlineStr">
+        <is>
+          <t>PO-0025</t>
+        </is>
+      </c>
       <c r="P63" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -34819,13 +34856,17 @@
       </c>
       <c r="N65" s="10" t="inlineStr">
         <is>
-          <t>CMP-SAE103</t>
-        </is>
-      </c>
-      <c r="O65" s="10" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O65" s="10" t="inlineStr">
+        <is>
+          <t>PO-0026</t>
+        </is>
+      </c>
       <c r="P65" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -34881,13 +34922,17 @@
       </c>
       <c r="N66" s="10" t="inlineStr">
         <is>
-          <t>CMP-SAE103</t>
-        </is>
-      </c>
-      <c r="O66" s="10" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O66" s="10" t="inlineStr">
+        <is>
+          <t>PO-0027</t>
+        </is>
+      </c>
       <c r="P66" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>

--- a/APS_BF_SMS_RM.xlsx
+++ b/APS_BF_SMS_RM.xlsx
@@ -30933,7 +30933,7 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>PO-0036</t>
+          <t>PO-0034</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr">
@@ -30999,7 +30999,7 @@
       </c>
       <c r="O6" s="10" t="inlineStr">
         <is>
-          <t>PO-0009</t>
+          <t>PO-0021</t>
         </is>
       </c>
       <c r="P6" s="10" t="inlineStr">
@@ -31131,7 +31131,7 @@
       </c>
       <c r="O8" s="10" t="inlineStr">
         <is>
-          <t>PO-0018</t>
+          <t>PO-0017</t>
         </is>
       </c>
       <c r="P8" s="10" t="inlineStr">
@@ -31258,13 +31258,17 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE106</t>
-        </is>
-      </c>
-      <c r="O10" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>PO-0038</t>
+        </is>
+      </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -31457,7 +31461,7 @@
       </c>
       <c r="O13" s="10" t="inlineStr">
         <is>
-          <t>PO-0014</t>
+          <t>PO-0013</t>
         </is>
       </c>
       <c r="P13" s="10" t="inlineStr">
@@ -31518,13 +31522,17 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE106</t>
-        </is>
-      </c>
-      <c r="O14" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>PO-0030</t>
+        </is>
+      </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -31585,7 +31593,7 @@
       </c>
       <c r="O15" s="10" t="inlineStr">
         <is>
-          <t>PO-0013</t>
+          <t>PO-0012</t>
         </is>
       </c>
       <c r="P15" s="10" t="inlineStr">
@@ -31646,13 +31654,17 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE106</t>
-        </is>
-      </c>
-      <c r="O16" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>PO-0038</t>
+        </is>
+      </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -31840,13 +31852,17 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE101</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>PO-0037</t>
+        </is>
+      </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -31973,7 +31989,7 @@
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>PO-0034</t>
+          <t>PO-0032</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
@@ -32039,7 +32055,7 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>PO-0032</t>
+          <t>PO-0030</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr">
@@ -32105,7 +32121,7 @@
       </c>
       <c r="O23" s="10" t="inlineStr">
         <is>
-          <t>PO-0012</t>
+          <t>PO-0011</t>
         </is>
       </c>
       <c r="P23" s="10" t="inlineStr">
@@ -32171,7 +32187,7 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>PO-0021</t>
+          <t>PO-0020</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
@@ -32237,7 +32253,7 @@
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>PO-0033</t>
+          <t>PO-0031</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
@@ -32298,13 +32314,17 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE101</t>
-        </is>
-      </c>
-      <c r="O26" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>PO-0025</t>
+        </is>
+      </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -32431,7 +32451,7 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>PO-0030</t>
+          <t>PO-0021</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
@@ -32563,7 +32583,7 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>PO-0035</t>
+          <t>PO-0033</t>
         </is>
       </c>
       <c r="P30" s="4" t="inlineStr">
@@ -32761,7 +32781,7 @@
       </c>
       <c r="O33" s="10" t="inlineStr">
         <is>
-          <t>PO-0010</t>
+          <t>PO-0009</t>
         </is>
       </c>
       <c r="P33" s="10" t="inlineStr">
@@ -32827,7 +32847,7 @@
       </c>
       <c r="O34" s="10" t="inlineStr">
         <is>
-          <t>PO-0011</t>
+          <t>PO-0010</t>
         </is>
       </c>
       <c r="P34" s="10" t="inlineStr">
@@ -32893,7 +32913,7 @@
       </c>
       <c r="O35" s="10" t="inlineStr">
         <is>
-          <t>PO-0015</t>
+          <t>PO-0014</t>
         </is>
       </c>
       <c r="P35" s="10" t="inlineStr">
@@ -32959,7 +32979,7 @@
       </c>
       <c r="O36" s="10" t="inlineStr">
         <is>
-          <t>PO-0019</t>
+          <t>PO-0018</t>
         </is>
       </c>
       <c r="P36" s="10" t="inlineStr">
@@ -33355,7 +33375,7 @@
       </c>
       <c r="O42" s="10" t="inlineStr">
         <is>
-          <t>PO-0020</t>
+          <t>PO-0019</t>
         </is>
       </c>
       <c r="P42" s="10" t="inlineStr">
@@ -33487,7 +33507,7 @@
       </c>
       <c r="O44" s="10" t="inlineStr">
         <is>
-          <t>PO-0018</t>
+          <t>PO-0017</t>
         </is>
       </c>
       <c r="P44" s="10" t="inlineStr">
@@ -33553,7 +33573,7 @@
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>PO-0031</t>
+          <t>PO-0027</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
@@ -33680,17 +33700,17 @@
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE101</t>
+          <t>APS_RELEASED</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>BIG-1018</t>
+          <t>PO-0036</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -33746,17 +33766,17 @@
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE101</t>
+          <t>APS_RELEASED</t>
         </is>
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>BIG-1018</t>
+          <t>PO-0036</t>
         </is>
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -33817,7 +33837,7 @@
       </c>
       <c r="O49" s="10" t="inlineStr">
         <is>
-          <t>PO-0012</t>
+          <t>PO-0011</t>
         </is>
       </c>
       <c r="P49" s="10" t="inlineStr">
@@ -33949,7 +33969,7 @@
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>PO-0009</t>
+          <t>PO-0002</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
@@ -34081,7 +34101,7 @@
       </c>
       <c r="O53" s="10" t="inlineStr">
         <is>
-          <t>PO-0016</t>
+          <t>PO-0015</t>
         </is>
       </c>
       <c r="P53" s="10" t="inlineStr">
@@ -34147,7 +34167,7 @@
       </c>
       <c r="O54" s="10" t="inlineStr">
         <is>
-          <t>PO-0013</t>
+          <t>PO-0012</t>
         </is>
       </c>
       <c r="P54" s="10" t="inlineStr">
@@ -34213,7 +34233,7 @@
       </c>
       <c r="O55" s="10" t="inlineStr">
         <is>
-          <t>PO-0017</t>
+          <t>PO-0016</t>
         </is>
       </c>
       <c r="P55" s="10" t="inlineStr">
@@ -34279,7 +34299,7 @@
       </c>
       <c r="O56" s="10" t="inlineStr">
         <is>
-          <t>PO-0014</t>
+          <t>PO-0013</t>
         </is>
       </c>
       <c r="P56" s="10" t="inlineStr">
@@ -34345,7 +34365,7 @@
       </c>
       <c r="O57" s="10" t="inlineStr">
         <is>
-          <t>PO-0020</t>
+          <t>PO-0019</t>
         </is>
       </c>
       <c r="P57" s="10" t="inlineStr">
@@ -34477,7 +34497,7 @@
       </c>
       <c r="O59" s="10" t="inlineStr">
         <is>
-          <t>PO-0021</t>
+          <t>PO-0020</t>
         </is>
       </c>
       <c r="P59" s="10" t="inlineStr">
@@ -34543,7 +34563,7 @@
       </c>
       <c r="O60" s="10" t="inlineStr">
         <is>
-          <t>PO-0010</t>
+          <t>PO-0009</t>
         </is>
       </c>
       <c r="P60" s="10" t="inlineStr">
@@ -34666,13 +34686,17 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE100</t>
-        </is>
-      </c>
-      <c r="O62" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O62" s="4" t="inlineStr">
+        <is>
+          <t>PO-0035</t>
+        </is>
+      </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -34794,13 +34818,17 @@
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE101</t>
-        </is>
-      </c>
-      <c r="O64" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O64" s="4" t="inlineStr">
+        <is>
+          <t>PO-0033</t>
+        </is>
+      </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -35112,13 +35140,17 @@
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE108</t>
-        </is>
-      </c>
-      <c r="O69" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O69" s="4" t="inlineStr">
+        <is>
+          <t>PO-0034</t>
+        </is>
+      </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>

--- a/APS_BF_SMS_RM.xlsx
+++ b/APS_BF_SMS_RM.xlsx
@@ -8549,7 +8549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18" customWidth="1" style="35" min="1" max="4"/>
@@ -8933,6 +8933,23 @@
       <c r="D19" t="inlineStr">
         <is>
           <t>2026-05-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>REQ-1776050729715</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FG-WR-SAE1008-80</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -30867,7 +30884,7 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>PO-0025</t>
+          <t>PO-0004</t>
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr">
@@ -30933,7 +30950,7 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>PO-0034</t>
+          <t>PO-0005</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr">
@@ -30999,7 +31016,7 @@
       </c>
       <c r="O6" s="10" t="inlineStr">
         <is>
-          <t>PO-0021</t>
+          <t>PO-0002</t>
         </is>
       </c>
       <c r="P6" s="10" t="inlineStr">
@@ -31065,7 +31082,7 @@
       </c>
       <c r="O7" s="11" t="inlineStr">
         <is>
-          <t>PO-0007</t>
+          <t>PO-0001</t>
         </is>
       </c>
       <c r="P7" s="11" t="inlineStr">
@@ -31131,7 +31148,7 @@
       </c>
       <c r="O8" s="10" t="inlineStr">
         <is>
-          <t>PO-0017</t>
+          <t>PO-0003</t>
         </is>
       </c>
       <c r="P8" s="10" t="inlineStr">
@@ -31197,7 +31214,7 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>PO-0027</t>
+          <t>PO-0030</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
@@ -31263,7 +31280,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>PO-0038</t>
+          <t>PO-0039</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
@@ -31527,7 +31544,7 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>PO-0030</t>
+          <t>PO-0031</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
@@ -31659,7 +31676,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>PO-0038</t>
+          <t>PO-0039</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
@@ -31857,7 +31874,7 @@
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>PO-0037</t>
+          <t>PO-0038</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
@@ -31989,7 +32006,7 @@
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>PO-0032</t>
+          <t>PO-0033</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
@@ -32055,7 +32072,7 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>PO-0030</t>
+          <t>PO-0031</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr">
@@ -32253,7 +32270,7 @@
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>PO-0031</t>
+          <t>PO-0032</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
@@ -32583,7 +32600,7 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>PO-0033</t>
+          <t>PO-0034</t>
         </is>
       </c>
       <c r="P30" s="4" t="inlineStr">
@@ -33573,7 +33590,7 @@
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>PO-0027</t>
+          <t>PO-0030</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
@@ -33705,7 +33722,7 @@
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>PO-0036</t>
+          <t>PO-0037</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
@@ -33771,7 +33788,7 @@
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>PO-0036</t>
+          <t>PO-0037</t>
         </is>
       </c>
       <c r="P48" s="4" t="inlineStr">
@@ -34624,13 +34641,17 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE100</t>
-        </is>
-      </c>
-      <c r="O61" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O61" s="4" t="inlineStr">
+        <is>
+          <t>PO-0041</t>
+        </is>
+      </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -34691,7 +34712,7 @@
       </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t>PO-0035</t>
+          <t>PO-0036</t>
         </is>
       </c>
       <c r="P62" s="4" t="inlineStr">
@@ -34823,7 +34844,7 @@
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t>PO-0033</t>
+          <t>PO-0034</t>
         </is>
       </c>
       <c r="P64" s="4" t="inlineStr">
@@ -35016,13 +35037,17 @@
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE104</t>
-        </is>
-      </c>
-      <c r="O67" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O67" s="4" t="inlineStr">
+        <is>
+          <t>PO-0042</t>
+        </is>
+      </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -35078,13 +35103,17 @@
       </c>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE106</t>
-        </is>
-      </c>
-      <c r="O68" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O68" s="4" t="inlineStr">
+        <is>
+          <t>PO-0039</t>
+        </is>
+      </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -35145,7 +35174,7 @@
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>PO-0034</t>
+          <t>PO-0035</t>
         </is>
       </c>
       <c r="P69" s="4" t="inlineStr">
@@ -35206,13 +35235,17 @@
       </c>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>CMP-CHQ100</t>
-        </is>
-      </c>
-      <c r="O70" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O70" s="4" t="inlineStr">
+        <is>
+          <t>PO-0040</t>
+        </is>
+      </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -35268,13 +35301,17 @@
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE100</t>
-        </is>
-      </c>
-      <c r="O71" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O71" s="4" t="inlineStr">
+        <is>
+          <t>PO-0001</t>
+        </is>
+      </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -35330,13 +35367,17 @@
       </c>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE100</t>
-        </is>
-      </c>
-      <c r="O72" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O72" s="4" t="inlineStr">
+        <is>
+          <t>PO-0005</t>
+        </is>
+      </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -35392,13 +35433,17 @@
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE101</t>
-        </is>
-      </c>
-      <c r="O73" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O73" s="4" t="inlineStr">
+        <is>
+          <t>PO-0006</t>
+        </is>
+      </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -35454,13 +35499,17 @@
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE101</t>
-        </is>
-      </c>
-      <c r="O74" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O74" s="4" t="inlineStr">
+        <is>
+          <t>PO-0002</t>
+        </is>
+      </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -35516,13 +35565,17 @@
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE103</t>
-        </is>
-      </c>
-      <c r="O75" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O75" s="4" t="inlineStr">
+        <is>
+          <t>PO-0007</t>
+        </is>
+      </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -35578,13 +35631,17 @@
       </c>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE103</t>
-        </is>
-      </c>
-      <c r="O76" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O76" s="4" t="inlineStr">
+        <is>
+          <t>PO-0003</t>
+        </is>
+      </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -35640,13 +35697,17 @@
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE104</t>
-        </is>
-      </c>
-      <c r="O77" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O77" s="4" t="inlineStr">
+        <is>
+          <t>PO-0010</t>
+        </is>
+      </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -35702,13 +35763,17 @@
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE106</t>
-        </is>
-      </c>
-      <c r="O78" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O78" s="4" t="inlineStr">
+        <is>
+          <t>PO-0008</t>
+        </is>
+      </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -35764,13 +35829,17 @@
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>CMP-SAE108</t>
-        </is>
-      </c>
-      <c r="O79" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O79" s="4" t="inlineStr">
+        <is>
+          <t>PO-0009</t>
+        </is>
+      </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -35826,13 +35895,17 @@
       </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>CMP-CHQ100</t>
-        </is>
-      </c>
-      <c r="O80" s="4" t="n"/>
+          <t>APS_RELEASED</t>
+        </is>
+      </c>
+      <c r="O80" s="4" t="inlineStr">
+        <is>
+          <t>PO-0004</t>
+        </is>
+      </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
